--- a/Estimacion_error/datos_aves_marinas/2025/abril/Rompeolas/conteos_reales.xlsx
+++ b/Estimacion_error/datos_aves_marinas/2025/abril/Rompeolas/conteos_reales.xlsx
@@ -1,26 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2025\abril\Rompeolas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Data_Saiensss\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2025\abril\Rompeolas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFBE7361-4BCA-40B4-BF62-3B6C201183D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97593A8A-1E53-4323-9502-928073946047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$M$3:$Q$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$340</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="21">
   <si>
     <t>FOTO</t>
   </si>
@@ -69,12 +88,27 @@
   <si>
     <t>gallinazo cabeza roja adulto</t>
   </si>
+  <si>
+    <t>x_0.20</t>
+  </si>
+  <si>
+    <t>abs(erorr)</t>
+  </si>
+  <si>
+    <t>MAE</t>
+  </si>
+  <si>
+    <t>Smape</t>
+  </si>
+  <si>
+    <t>sMAPE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -84,6 +118,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -108,17 +149,20 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -134,9 +178,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -174,9 +218,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -209,9 +253,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -244,9 +305,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -420,13 +498,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C340"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -437,7 +516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>222</v>
       </c>
@@ -448,7 +527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>222</v>
       </c>
@@ -459,7 +538,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>362</v>
       </c>
@@ -470,7 +549,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>371</v>
       </c>
@@ -481,7 +560,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>378</v>
       </c>
@@ -492,7 +571,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>380</v>
       </c>
@@ -503,7 +582,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>380</v>
       </c>
@@ -514,7 +593,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>380</v>
       </c>
@@ -525,7 +604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>384</v>
       </c>
@@ -536,7 +615,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>384</v>
       </c>
@@ -547,7 +626,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>384</v>
       </c>
@@ -558,7 +637,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>384</v>
       </c>
@@ -569,7 +648,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>389</v>
       </c>
@@ -580,7 +659,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>389</v>
       </c>
@@ -591,7 +670,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>389</v>
       </c>
@@ -602,7 +681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>392</v>
       </c>
@@ -613,7 +692,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>393</v>
       </c>
@@ -624,7 +703,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>393</v>
       </c>
@@ -635,7 +714,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>397</v>
       </c>
@@ -646,7 +725,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>397</v>
       </c>
@@ -657,7 +736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>397</v>
       </c>
@@ -668,7 +747,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>397</v>
       </c>
@@ -679,7 +758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>397</v>
       </c>
@@ -690,7 +769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>402</v>
       </c>
@@ -701,7 +780,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>402</v>
       </c>
@@ -712,7 +791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>402</v>
       </c>
@@ -723,7 +802,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>402</v>
       </c>
@@ -734,7 +813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>402</v>
       </c>
@@ -745,7 +824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>405</v>
       </c>
@@ -756,7 +835,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>405</v>
       </c>
@@ -767,7 +846,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>405</v>
       </c>
@@ -778,7 +857,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>405</v>
       </c>
@@ -789,7 +868,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>408</v>
       </c>
@@ -800,7 +879,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>408</v>
       </c>
@@ -811,7 +890,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>408</v>
       </c>
@@ -822,7 +901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>408</v>
       </c>
@@ -833,7 +912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>411</v>
       </c>
@@ -844,7 +923,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>411</v>
       </c>
@@ -855,7 +934,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>416</v>
       </c>
@@ -866,7 +945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>416</v>
       </c>
@@ -877,7 +956,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>416</v>
       </c>
@@ -888,7 +967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>416</v>
       </c>
@@ -899,7 +978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>419</v>
       </c>
@@ -910,7 +989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>419</v>
       </c>
@@ -921,7 +1000,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>419</v>
       </c>
@@ -932,7 +1011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>419</v>
       </c>
@@ -943,7 +1022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>422</v>
       </c>
@@ -954,7 +1033,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>422</v>
       </c>
@@ -965,7 +1044,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>425</v>
       </c>
@@ -976,7 +1055,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>425</v>
       </c>
@@ -987,7 +1066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>425</v>
       </c>
@@ -998,7 +1077,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>425</v>
       </c>
@@ -1009,7 +1088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>425</v>
       </c>
@@ -1020,7 +1099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>428</v>
       </c>
@@ -1031,7 +1110,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>428</v>
       </c>
@@ -1042,7 +1121,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>428</v>
       </c>
@@ -1053,7 +1132,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>428</v>
       </c>
@@ -1064,7 +1143,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>431</v>
       </c>
@@ -1075,7 +1154,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>431</v>
       </c>
@@ -1086,7 +1165,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>431</v>
       </c>
@@ -1097,7 +1176,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>431</v>
       </c>
@@ -1108,7 +1187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>433</v>
       </c>
@@ -1119,7 +1198,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>433</v>
       </c>
@@ -1130,7 +1209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>433</v>
       </c>
@@ -1141,7 +1220,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>433</v>
       </c>
@@ -1152,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>436</v>
       </c>
@@ -1163,7 +1242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>436</v>
       </c>
@@ -1174,7 +1253,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>436</v>
       </c>
@@ -1185,7 +1264,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>436</v>
       </c>
@@ -1196,7 +1275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>436</v>
       </c>
@@ -1207,7 +1286,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>436</v>
       </c>
@@ -1218,7 +1297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>440</v>
       </c>
@@ -1229,7 +1308,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>440</v>
       </c>
@@ -1240,7 +1319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>440</v>
       </c>
@@ -1251,7 +1330,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>440</v>
       </c>
@@ -1262,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>440</v>
       </c>
@@ -1273,7 +1352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>443</v>
       </c>
@@ -1284,7 +1363,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>443</v>
       </c>
@@ -1295,7 +1374,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>443</v>
       </c>
@@ -1306,7 +1385,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>443</v>
       </c>
@@ -1317,7 +1396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>446</v>
       </c>
@@ -1328,7 +1407,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>446</v>
       </c>
@@ -1339,7 +1418,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>446</v>
       </c>
@@ -1350,7 +1429,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>446</v>
       </c>
@@ -1361,7 +1440,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>446</v>
       </c>
@@ -1372,7 +1451,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>450</v>
       </c>
@@ -1383,7 +1462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>450</v>
       </c>
@@ -1394,7 +1473,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>450</v>
       </c>
@@ -1405,7 +1484,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>450</v>
       </c>
@@ -1416,7 +1495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>450</v>
       </c>
@@ -1427,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>450</v>
       </c>
@@ -1438,7 +1517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>453</v>
       </c>
@@ -1449,7 +1528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>453</v>
       </c>
@@ -1460,7 +1539,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>453</v>
       </c>
@@ -1471,7 +1550,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>453</v>
       </c>
@@ -1482,7 +1561,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>455</v>
       </c>
@@ -1493,7 +1572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>455</v>
       </c>
@@ -1504,7 +1583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>455</v>
       </c>
@@ -1515,7 +1594,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>455</v>
       </c>
@@ -1526,7 +1605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>455</v>
       </c>
@@ -1537,7 +1616,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>455</v>
       </c>
@@ -1548,7 +1627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>458</v>
       </c>
@@ -1559,7 +1638,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>458</v>
       </c>
@@ -1570,7 +1649,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>458</v>
       </c>
@@ -1581,7 +1660,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>458</v>
       </c>
@@ -1592,7 +1671,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>458</v>
       </c>
@@ -1603,7 +1682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>461</v>
       </c>
@@ -1614,7 +1693,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>461</v>
       </c>
@@ -1625,7 +1704,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>461</v>
       </c>
@@ -1636,7 +1715,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>461</v>
       </c>
@@ -1647,7 +1726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>466</v>
       </c>
@@ -1658,7 +1737,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>466</v>
       </c>
@@ -1669,7 +1748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>466</v>
       </c>
@@ -1680,7 +1759,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>466</v>
       </c>
@@ -1691,7 +1770,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>466</v>
       </c>
@@ -1702,7 +1781,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>466</v>
       </c>
@@ -1713,7 +1792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>466</v>
       </c>
@@ -1724,7 +1803,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>470</v>
       </c>
@@ -1735,7 +1814,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>470</v>
       </c>
@@ -1746,7 +1825,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>470</v>
       </c>
@@ -1757,7 +1836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>470</v>
       </c>
@@ -1768,7 +1847,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>470</v>
       </c>
@@ -1779,7 +1858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>470</v>
       </c>
@@ -1790,7 +1869,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>473</v>
       </c>
@@ -1801,7 +1880,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>473</v>
       </c>
@@ -1812,7 +1891,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>473</v>
       </c>
@@ -1823,7 +1902,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>473</v>
       </c>
@@ -1834,7 +1913,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>475</v>
       </c>
@@ -1845,7 +1924,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>475</v>
       </c>
@@ -1856,7 +1935,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>475</v>
       </c>
@@ -1867,7 +1946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>475</v>
       </c>
@@ -1878,7 +1957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>475</v>
       </c>
@@ -1889,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>478</v>
       </c>
@@ -1900,7 +1979,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>478</v>
       </c>
@@ -1911,7 +1990,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>478</v>
       </c>
@@ -1922,7 +2001,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>478</v>
       </c>
@@ -1933,7 +2012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>478</v>
       </c>
@@ -1944,7 +2023,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>481</v>
       </c>
@@ -1955,7 +2034,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>481</v>
       </c>
@@ -1966,7 +2045,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>481</v>
       </c>
@@ -1977,7 +2056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>481</v>
       </c>
@@ -1988,7 +2067,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>484</v>
       </c>
@@ -1999,7 +2078,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>484</v>
       </c>
@@ -2010,7 +2089,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>484</v>
       </c>
@@ -2021,7 +2100,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>484</v>
       </c>
@@ -2032,7 +2111,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>487</v>
       </c>
@@ -2043,7 +2122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>487</v>
       </c>
@@ -2054,7 +2133,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>487</v>
       </c>
@@ -2065,7 +2144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>487</v>
       </c>
@@ -2076,7 +2155,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>487</v>
       </c>
@@ -2087,7 +2166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>490</v>
       </c>
@@ -2098,7 +2177,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>490</v>
       </c>
@@ -2109,7 +2188,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>490</v>
       </c>
@@ -2120,7 +2199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>490</v>
       </c>
@@ -2131,7 +2210,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>490</v>
       </c>
@@ -2142,7 +2221,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>495</v>
       </c>
@@ -2153,7 +2232,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>495</v>
       </c>
@@ -2164,7 +2243,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>495</v>
       </c>
@@ -2175,7 +2254,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>495</v>
       </c>
@@ -2186,7 +2265,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>495</v>
       </c>
@@ -2197,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>495</v>
       </c>
@@ -2208,7 +2287,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>499</v>
       </c>
@@ -2219,7 +2298,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>499</v>
       </c>
@@ -2230,7 +2309,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>499</v>
       </c>
@@ -2241,7 +2320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>499</v>
       </c>
@@ -2252,7 +2331,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>499</v>
       </c>
@@ -2263,7 +2342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>499</v>
       </c>
@@ -2274,7 +2353,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>503</v>
       </c>
@@ -2285,7 +2364,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>503</v>
       </c>
@@ -2296,7 +2375,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>503</v>
       </c>
@@ -2307,7 +2386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>506</v>
       </c>
@@ -2318,7 +2397,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>506</v>
       </c>
@@ -2329,7 +2408,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>506</v>
       </c>
@@ -2340,7 +2419,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>506</v>
       </c>
@@ -2351,7 +2430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>506</v>
       </c>
@@ -2362,7 +2441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>506</v>
       </c>
@@ -2373,7 +2452,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>509</v>
       </c>
@@ -2384,7 +2463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>509</v>
       </c>
@@ -2395,7 +2474,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>509</v>
       </c>
@@ -2406,7 +2485,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>509</v>
       </c>
@@ -2417,7 +2496,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>512</v>
       </c>
@@ -2428,7 +2507,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>512</v>
       </c>
@@ -2439,7 +2518,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>512</v>
       </c>
@@ -2450,7 +2529,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>512</v>
       </c>
@@ -2461,7 +2540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>512</v>
       </c>
@@ -2472,7 +2551,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>512</v>
       </c>
@@ -2483,7 +2562,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>515</v>
       </c>
@@ -2494,7 +2573,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>515</v>
       </c>
@@ -2505,7 +2584,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>515</v>
       </c>
@@ -2516,7 +2595,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>518</v>
       </c>
@@ -2527,7 +2606,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>518</v>
       </c>
@@ -2538,7 +2617,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>518</v>
       </c>
@@ -2549,7 +2628,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>521</v>
       </c>
@@ -2560,7 +2639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>521</v>
       </c>
@@ -2571,7 +2650,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>525</v>
       </c>
@@ -2582,7 +2661,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>525</v>
       </c>
@@ -2593,7 +2672,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>529</v>
       </c>
@@ -2604,7 +2683,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>529</v>
       </c>
@@ -2615,7 +2694,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>529</v>
       </c>
@@ -2626,7 +2705,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>529</v>
       </c>
@@ -2637,7 +2716,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>529</v>
       </c>
@@ -2648,7 +2727,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>533</v>
       </c>
@@ -2659,7 +2738,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>533</v>
       </c>
@@ -2670,7 +2749,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>533</v>
       </c>
@@ -2681,7 +2760,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>536</v>
       </c>
@@ -2692,7 +2771,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>545</v>
       </c>
@@ -2703,7 +2782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>545</v>
       </c>
@@ -2714,7 +2793,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>547</v>
       </c>
@@ -2725,7 +2804,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>547</v>
       </c>
@@ -2736,7 +2815,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>547</v>
       </c>
@@ -2747,7 +2826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>547</v>
       </c>
@@ -2758,7 +2837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>550</v>
       </c>
@@ -2769,7 +2848,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>550</v>
       </c>
@@ -2780,7 +2859,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>550</v>
       </c>
@@ -2791,7 +2870,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>553</v>
       </c>
@@ -2802,7 +2881,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>553</v>
       </c>
@@ -2813,7 +2892,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>553</v>
       </c>
@@ -2824,7 +2903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>556</v>
       </c>
@@ -2835,7 +2914,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>556</v>
       </c>
@@ -2846,7 +2925,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>558</v>
       </c>
@@ -2857,7 +2936,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>561</v>
       </c>
@@ -2868,7 +2947,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>561</v>
       </c>
@@ -2879,7 +2958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>561</v>
       </c>
@@ -2890,7 +2969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>564</v>
       </c>
@@ -2901,7 +2980,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>564</v>
       </c>
@@ -2912,7 +2991,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>567</v>
       </c>
@@ -2923,7 +3002,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>567</v>
       </c>
@@ -2934,7 +3013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>569</v>
       </c>
@@ -2945,7 +3024,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>569</v>
       </c>
@@ -2956,7 +3035,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>572</v>
       </c>
@@ -2967,7 +3046,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>572</v>
       </c>
@@ -2978,7 +3057,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>574</v>
       </c>
@@ -2989,7 +3068,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>574</v>
       </c>
@@ -3000,7 +3079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>576</v>
       </c>
@@ -3011,7 +3090,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>576</v>
       </c>
@@ -3022,7 +3101,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>577</v>
       </c>
@@ -3033,7 +3112,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>577</v>
       </c>
@@ -3044,7 +3123,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>580</v>
       </c>
@@ -3055,7 +3134,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>580</v>
       </c>
@@ -3066,7 +3145,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>584</v>
       </c>
@@ -3077,7 +3156,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>584</v>
       </c>
@@ -3088,7 +3167,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>586</v>
       </c>
@@ -3099,7 +3178,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>586</v>
       </c>
@@ -3110,7 +3189,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>587</v>
       </c>
@@ -3121,7 +3200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>587</v>
       </c>
@@ -3132,7 +3211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>589</v>
       </c>
@@ -3143,7 +3222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>589</v>
       </c>
@@ -3154,7 +3233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>589</v>
       </c>
@@ -3165,7 +3244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>592</v>
       </c>
@@ -3176,7 +3255,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>592</v>
       </c>
@@ -3187,7 +3266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>594</v>
       </c>
@@ -3198,7 +3277,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>594</v>
       </c>
@@ -3209,7 +3288,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>596</v>
       </c>
@@ -3220,7 +3299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>596</v>
       </c>
@@ -3231,7 +3310,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>598</v>
       </c>
@@ -3242,7 +3321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>601</v>
       </c>
@@ -3253,7 +3332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>601</v>
       </c>
@@ -3264,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>603</v>
       </c>
@@ -3275,7 +3354,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>606</v>
       </c>
@@ -3286,7 +3365,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>606</v>
       </c>
@@ -3297,7 +3376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>609</v>
       </c>
@@ -3308,7 +3387,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>612</v>
       </c>
@@ -3319,7 +3398,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>615</v>
       </c>
@@ -3330,7 +3409,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>618</v>
       </c>
@@ -3341,7 +3420,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>618</v>
       </c>
@@ -3352,7 +3431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>621</v>
       </c>
@@ -3363,7 +3442,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>621</v>
       </c>
@@ -3374,7 +3453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>624</v>
       </c>
@@ -3385,7 +3464,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>624</v>
       </c>
@@ -3396,7 +3475,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>624</v>
       </c>
@@ -3407,7 +3486,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>627</v>
       </c>
@@ -3418,7 +3497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>627</v>
       </c>
@@ -3429,7 +3508,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>627</v>
       </c>
@@ -3440,7 +3519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>628</v>
       </c>
@@ -3451,7 +3530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>628</v>
       </c>
@@ -3462,7 +3541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>633</v>
       </c>
@@ -3473,7 +3552,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>633</v>
       </c>
@@ -3484,7 +3563,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>637</v>
       </c>
@@ -3495,7 +3574,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>637</v>
       </c>
@@ -3506,7 +3585,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>640</v>
       </c>
@@ -3517,7 +3596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>640</v>
       </c>
@@ -3528,7 +3607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>645</v>
       </c>
@@ -3539,7 +3618,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>645</v>
       </c>
@@ -3550,7 +3629,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>648</v>
       </c>
@@ -3561,7 +3640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>648</v>
       </c>
@@ -3572,7 +3651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>648</v>
       </c>
@@ -3583,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>651</v>
       </c>
@@ -3594,7 +3673,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>651</v>
       </c>
@@ -3605,7 +3684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>655</v>
       </c>
@@ -3616,7 +3695,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>655</v>
       </c>
@@ -3627,7 +3706,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>655</v>
       </c>
@@ -3638,7 +3717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>661</v>
       </c>
@@ -3649,7 +3728,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>661</v>
       </c>
@@ -3660,7 +3739,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>664</v>
       </c>
@@ -3671,7 +3750,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="296" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>664</v>
       </c>
@@ -3682,7 +3761,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>669</v>
       </c>
@@ -3693,7 +3772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>669</v>
       </c>
@@ -3704,7 +3783,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>672</v>
       </c>
@@ -3715,7 +3794,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>672</v>
       </c>
@@ -3726,7 +3805,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>676</v>
       </c>
@@ -3737,7 +3816,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>676</v>
       </c>
@@ -3748,7 +3827,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>678</v>
       </c>
@@ -3759,7 +3838,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>678</v>
       </c>
@@ -3770,7 +3849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>681</v>
       </c>
@@ -3781,7 +3860,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>681</v>
       </c>
@@ -3792,7 +3871,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>684</v>
       </c>
@@ -3803,7 +3882,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>684</v>
       </c>
@@ -3814,7 +3893,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>689</v>
       </c>
@@ -3825,7 +3904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>689</v>
       </c>
@@ -3836,7 +3915,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>693</v>
       </c>
@@ -3847,7 +3926,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>693</v>
       </c>
@@ -3858,7 +3937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>696</v>
       </c>
@@ -3869,7 +3948,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>699</v>
       </c>
@@ -3880,7 +3959,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>702</v>
       </c>
@@ -3891,7 +3970,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>702</v>
       </c>
@@ -3902,7 +3981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>705</v>
       </c>
@@ -3913,7 +3992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>709</v>
       </c>
@@ -3924,7 +4003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>712</v>
       </c>
@@ -3935,7 +4014,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>712</v>
       </c>
@@ -3946,7 +4025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>712</v>
       </c>
@@ -3957,7 +4036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>716</v>
       </c>
@@ -3968,7 +4047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>716</v>
       </c>
@@ -3979,7 +4058,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>718</v>
       </c>
@@ -3990,7 +4069,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>721</v>
       </c>
@@ -4001,7 +4080,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>721</v>
       </c>
@@ -4012,7 +4091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>723</v>
       </c>
@@ -4023,7 +4102,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>723</v>
       </c>
@@ -4034,7 +4113,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>723</v>
       </c>
@@ -4045,7 +4124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>725</v>
       </c>
@@ -4056,7 +4135,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>725</v>
       </c>
@@ -4067,7 +4146,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>725</v>
       </c>
@@ -4078,7 +4157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>728</v>
       </c>
@@ -4089,7 +4168,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>728</v>
       </c>
@@ -4100,7 +4179,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>731</v>
       </c>
@@ -4111,7 +4190,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>731</v>
       </c>
@@ -4122,7 +4201,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>734</v>
       </c>
@@ -4133,7 +4212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>734</v>
       </c>
@@ -4144,7 +4223,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>734</v>
       </c>
@@ -4155,7 +4234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>738</v>
       </c>
@@ -4167,6 +4246,3430 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C340" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="zarcillo"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA55525-5725-432D-8CC7-0A0B7E5373EF}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="D2:Q119"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>0</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D3">
+        <v>222</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="M3" t="s">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>16</v>
+      </c>
+      <c r="O3" t="s">
+        <v>2</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D4">
+        <v>362</v>
+      </c>
+      <c r="E4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4">
+        <v>9</v>
+      </c>
+      <c r="M4">
+        <v>371</v>
+      </c>
+      <c r="N4">
+        <v>28</v>
+      </c>
+      <c r="O4">
+        <f>VLOOKUP(M4,$D$2:$F$119,3,FALSE)</f>
+        <v>33</v>
+      </c>
+      <c r="P4">
+        <f>ABS(N4-O4)</f>
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <f>P4/(N4+O4)*2</f>
+        <v>0.16393442622950818</v>
+      </c>
+    </row>
+    <row r="5" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D5">
+        <v>371</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>33</v>
+      </c>
+      <c r="M5">
+        <v>378</v>
+      </c>
+      <c r="N5">
+        <v>35</v>
+      </c>
+      <c r="O5">
+        <f t="shared" ref="O5:O68" si="0">VLOOKUP(M5,$D$2:$F$119,3,FALSE)</f>
+        <v>51</v>
+      </c>
+      <c r="P5">
+        <f t="shared" ref="P5:P68" si="1">ABS(N5-O5)</f>
+        <v>16</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" ref="Q5:Q68" si="2">P5/(N5+O5)*2</f>
+        <v>0.37209302325581395</v>
+      </c>
+    </row>
+    <row r="6" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D6">
+        <v>378</v>
+      </c>
+      <c r="E6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>51</v>
+      </c>
+      <c r="M6">
+        <v>380</v>
+      </c>
+      <c r="N6">
+        <v>44</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="P6">
+        <f t="shared" si="1"/>
+        <v>50</v>
+      </c>
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.72463768115942029</v>
+      </c>
+    </row>
+    <row r="7" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D7">
+        <v>380</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>94</v>
+      </c>
+      <c r="H7" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7">
+        <f>AVERAGE(P4:P118)</f>
+        <v>15.443478260869565</v>
+      </c>
+      <c r="M7">
+        <v>384</v>
+      </c>
+      <c r="N7">
+        <v>113</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>147</v>
+      </c>
+      <c r="P7">
+        <f t="shared" si="1"/>
+        <v>34</v>
+      </c>
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.26153846153846155</v>
+      </c>
+    </row>
+    <row r="8" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D8">
+        <v>384</v>
+      </c>
+      <c r="E8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>147</v>
+      </c>
+      <c r="H8" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="2">
+        <f>AVERAGE(Q4:Q118)</f>
+        <v>0.21140313113907816</v>
+      </c>
+      <c r="M8">
+        <v>389</v>
+      </c>
+      <c r="N8">
+        <v>107</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>172</v>
+      </c>
+      <c r="P8">
+        <f t="shared" si="1"/>
+        <v>65</v>
+      </c>
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.46594982078853048</v>
+      </c>
+    </row>
+    <row r="9" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D9">
+        <v>389</v>
+      </c>
+      <c r="E9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>172</v>
+      </c>
+      <c r="M9">
+        <v>393</v>
+      </c>
+      <c r="N9">
+        <v>124</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>191</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.42539682539682538</v>
+      </c>
+    </row>
+    <row r="10" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D10">
+        <v>393</v>
+      </c>
+      <c r="E10" t="s">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>191</v>
+      </c>
+      <c r="M10">
+        <v>397</v>
+      </c>
+      <c r="N10">
+        <v>155</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>196</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="1"/>
+        <v>41</v>
+      </c>
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.23361823361823361</v>
+      </c>
+    </row>
+    <row r="11" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D11">
+        <v>397</v>
+      </c>
+      <c r="E11" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11">
+        <v>196</v>
+      </c>
+      <c r="M11">
+        <v>402</v>
+      </c>
+      <c r="N11">
+        <v>151</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>186</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.20771513353115728</v>
+      </c>
+    </row>
+    <row r="12" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D12">
+        <v>402</v>
+      </c>
+      <c r="E12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F12">
+        <v>186</v>
+      </c>
+      <c r="M12">
+        <v>405</v>
+      </c>
+      <c r="N12">
+        <v>161</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>187</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="1"/>
+        <v>26</v>
+      </c>
+      <c r="Q12">
+        <f t="shared" si="2"/>
+        <v>0.14942528735632185</v>
+      </c>
+    </row>
+    <row r="13" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D13">
+        <v>405</v>
+      </c>
+      <c r="E13" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>187</v>
+      </c>
+      <c r="M13">
+        <v>408</v>
+      </c>
+      <c r="N13">
+        <v>201</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>220</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="1"/>
+        <v>19</v>
+      </c>
+      <c r="Q13">
+        <f t="shared" si="2"/>
+        <v>9.0261282660332537E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D14">
+        <v>408</v>
+      </c>
+      <c r="E14" t="s">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>220</v>
+      </c>
+      <c r="M14">
+        <v>411</v>
+      </c>
+      <c r="N14">
+        <v>167</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>194</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="1"/>
+        <v>27</v>
+      </c>
+      <c r="Q14">
+        <f t="shared" si="2"/>
+        <v>0.14958448753462603</v>
+      </c>
+    </row>
+    <row r="15" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D15">
+        <v>411</v>
+      </c>
+      <c r="E15" t="s">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>194</v>
+      </c>
+      <c r="M15">
+        <v>416</v>
+      </c>
+      <c r="N15">
+        <v>162</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>223</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="1"/>
+        <v>61</v>
+      </c>
+      <c r="Q15">
+        <f t="shared" si="2"/>
+        <v>0.31688311688311688</v>
+      </c>
+    </row>
+    <row r="16" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>416</v>
+      </c>
+      <c r="E16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16">
+        <v>223</v>
+      </c>
+      <c r="M16">
+        <v>419</v>
+      </c>
+      <c r="N16">
+        <v>171</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>419</v>
+      </c>
+      <c r="E17" t="s">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>171</v>
+      </c>
+      <c r="M17">
+        <v>422</v>
+      </c>
+      <c r="N17">
+        <v>159</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q17">
+        <f t="shared" si="2"/>
+        <v>7.2727272727272724E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>422</v>
+      </c>
+      <c r="E18" t="s">
+        <v>4</v>
+      </c>
+      <c r="F18">
+        <v>171</v>
+      </c>
+      <c r="M18">
+        <v>425</v>
+      </c>
+      <c r="N18">
+        <v>169</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="0"/>
+        <v>168</v>
+      </c>
+      <c r="P18">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <f t="shared" si="2"/>
+        <v>5.9347181008902079E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>425</v>
+      </c>
+      <c r="E19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19">
+        <v>168</v>
+      </c>
+      <c r="M19">
+        <v>428</v>
+      </c>
+      <c r="N19">
+        <v>131</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>149</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+      <c r="Q19">
+        <f t="shared" si="2"/>
+        <v>0.12857142857142856</v>
+      </c>
+    </row>
+    <row r="20" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>428</v>
+      </c>
+      <c r="E20" t="s">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>149</v>
+      </c>
+      <c r="M20">
+        <v>431</v>
+      </c>
+      <c r="N20">
+        <v>115</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>124</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q20">
+        <f t="shared" si="2"/>
+        <v>7.5313807531380755E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>431</v>
+      </c>
+      <c r="E21" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21">
+        <v>124</v>
+      </c>
+      <c r="M21">
+        <v>433</v>
+      </c>
+      <c r="N21">
+        <v>142</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="0"/>
+        <v>177</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="1"/>
+        <v>35</v>
+      </c>
+      <c r="Q21">
+        <f t="shared" si="2"/>
+        <v>0.21943573667711599</v>
+      </c>
+    </row>
+    <row r="22" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>433</v>
+      </c>
+      <c r="E22" t="s">
+        <v>4</v>
+      </c>
+      <c r="F22">
+        <v>177</v>
+      </c>
+      <c r="M22">
+        <v>436</v>
+      </c>
+      <c r="N22">
+        <v>163</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>230</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="1"/>
+        <v>67</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="2"/>
+        <v>0.34096692111959287</v>
+      </c>
+    </row>
+    <row r="23" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D23">
+        <v>436</v>
+      </c>
+      <c r="E23" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23">
+        <v>230</v>
+      </c>
+      <c r="M23">
+        <v>440</v>
+      </c>
+      <c r="N23">
+        <v>138</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>211</v>
+      </c>
+      <c r="P23">
+        <f t="shared" si="1"/>
+        <v>73</v>
+      </c>
+      <c r="Q23">
+        <f t="shared" si="2"/>
+        <v>0.41833810888252149</v>
+      </c>
+    </row>
+    <row r="24" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D24">
+        <v>440</v>
+      </c>
+      <c r="E24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F24">
+        <v>211</v>
+      </c>
+      <c r="M24">
+        <v>443</v>
+      </c>
+      <c r="N24">
+        <v>131</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="0"/>
+        <v>164</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="1"/>
+        <v>33</v>
+      </c>
+      <c r="Q24">
+        <f t="shared" si="2"/>
+        <v>0.22372881355932203</v>
+      </c>
+    </row>
+    <row r="25" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D25">
+        <v>443</v>
+      </c>
+      <c r="E25" t="s">
+        <v>4</v>
+      </c>
+      <c r="F25">
+        <v>164</v>
+      </c>
+      <c r="M25">
+        <v>446</v>
+      </c>
+      <c r="N25">
+        <v>134</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="0"/>
+        <v>221</v>
+      </c>
+      <c r="P25">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="Q25">
+        <f t="shared" si="2"/>
+        <v>0.49014084507042255</v>
+      </c>
+    </row>
+    <row r="26" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D26">
+        <v>446</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26">
+        <v>221</v>
+      </c>
+      <c r="M26">
+        <v>450</v>
+      </c>
+      <c r="N26">
+        <v>123</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="0"/>
+        <v>187</v>
+      </c>
+      <c r="P26">
+        <f t="shared" si="1"/>
+        <v>64</v>
+      </c>
+      <c r="Q26">
+        <f t="shared" si="2"/>
+        <v>0.41290322580645161</v>
+      </c>
+    </row>
+    <row r="27" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D27">
+        <v>450</v>
+      </c>
+      <c r="E27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27">
+        <v>187</v>
+      </c>
+      <c r="M27">
+        <v>453</v>
+      </c>
+      <c r="N27">
+        <v>63</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="0"/>
+        <v>94</v>
+      </c>
+      <c r="P27">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+      <c r="Q27">
+        <f t="shared" si="2"/>
+        <v>0.39490445859872614</v>
+      </c>
+    </row>
+    <row r="28" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D28">
+        <v>453</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28">
+        <v>94</v>
+      </c>
+      <c r="M28">
+        <v>455</v>
+      </c>
+      <c r="N28">
+        <v>134</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="0"/>
+        <v>234</v>
+      </c>
+      <c r="P28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="Q28">
+        <f t="shared" si="2"/>
+        <v>0.54347826086956519</v>
+      </c>
+    </row>
+    <row r="29" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D29">
+        <v>455</v>
+      </c>
+      <c r="E29" t="s">
+        <v>4</v>
+      </c>
+      <c r="F29">
+        <v>234</v>
+      </c>
+      <c r="M29">
+        <v>458</v>
+      </c>
+      <c r="N29">
+        <v>147</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="0"/>
+        <v>234</v>
+      </c>
+      <c r="P29">
+        <f t="shared" si="1"/>
+        <v>87</v>
+      </c>
+      <c r="Q29">
+        <f t="shared" si="2"/>
+        <v>0.45669291338582679</v>
+      </c>
+    </row>
+    <row r="30" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D30">
+        <v>458</v>
+      </c>
+      <c r="E30" t="s">
+        <v>4</v>
+      </c>
+      <c r="F30">
+        <v>234</v>
+      </c>
+      <c r="M30">
+        <v>461</v>
+      </c>
+      <c r="N30">
+        <v>200</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="0"/>
+        <v>203</v>
+      </c>
+      <c r="P30">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Q30">
+        <f t="shared" si="2"/>
+        <v>1.488833746898263E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D31">
+        <v>461</v>
+      </c>
+      <c r="E31" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31">
+        <v>203</v>
+      </c>
+      <c r="M31">
+        <v>466</v>
+      </c>
+      <c r="N31">
+        <v>178</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="0"/>
+        <v>255</v>
+      </c>
+      <c r="P31">
+        <f t="shared" si="1"/>
+        <v>77</v>
+      </c>
+      <c r="Q31">
+        <f t="shared" si="2"/>
+        <v>0.35565819861431869</v>
+      </c>
+    </row>
+    <row r="32" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D32">
+        <v>466</v>
+      </c>
+      <c r="E32" t="s">
+        <v>4</v>
+      </c>
+      <c r="F32">
+        <v>255</v>
+      </c>
+      <c r="M32">
+        <v>470</v>
+      </c>
+      <c r="N32">
+        <v>175</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="0"/>
+        <v>263</v>
+      </c>
+      <c r="P32">
+        <f t="shared" si="1"/>
+        <v>88</v>
+      </c>
+      <c r="Q32">
+        <f t="shared" si="2"/>
+        <v>0.40182648401826482</v>
+      </c>
+    </row>
+    <row r="33" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D33">
+        <v>470</v>
+      </c>
+      <c r="E33" t="s">
+        <v>4</v>
+      </c>
+      <c r="F33">
+        <v>263</v>
+      </c>
+      <c r="M33">
+        <v>473</v>
+      </c>
+      <c r="N33">
+        <v>168</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="P33">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <f t="shared" si="2"/>
+        <v>5.9701492537313433E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D34">
+        <v>473</v>
+      </c>
+      <c r="E34" t="s">
+        <v>4</v>
+      </c>
+      <c r="F34">
+        <v>167</v>
+      </c>
+      <c r="M34">
+        <v>475</v>
+      </c>
+      <c r="N34">
+        <v>284</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="0"/>
+        <v>263</v>
+      </c>
+      <c r="P34">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="Q34">
+        <f t="shared" si="2"/>
+        <v>7.6782449725776969E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D35">
+        <v>475</v>
+      </c>
+      <c r="E35" t="s">
+        <v>4</v>
+      </c>
+      <c r="F35">
+        <v>263</v>
+      </c>
+      <c r="M35">
+        <v>478</v>
+      </c>
+      <c r="N35">
+        <v>186</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="0"/>
+        <v>189</v>
+      </c>
+      <c r="P35">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+      <c r="Q35">
+        <f t="shared" si="2"/>
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D36">
+        <v>478</v>
+      </c>
+      <c r="E36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36">
+        <v>189</v>
+      </c>
+      <c r="M36">
+        <v>481</v>
+      </c>
+      <c r="N36">
+        <v>159</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="0"/>
+        <v>169</v>
+      </c>
+      <c r="P36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="Q36">
+        <f t="shared" si="2"/>
+        <v>6.097560975609756E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D37">
+        <v>481</v>
+      </c>
+      <c r="E37" t="s">
+        <v>4</v>
+      </c>
+      <c r="F37">
+        <v>169</v>
+      </c>
+      <c r="M37">
+        <v>484</v>
+      </c>
+      <c r="N37">
+        <v>172</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="0"/>
+        <v>181</v>
+      </c>
+      <c r="P37">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q37">
+        <f t="shared" si="2"/>
+        <v>5.0991501416430593E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D38">
+        <v>484</v>
+      </c>
+      <c r="E38" t="s">
+        <v>4</v>
+      </c>
+      <c r="F38">
+        <v>181</v>
+      </c>
+      <c r="M38">
+        <v>487</v>
+      </c>
+      <c r="N38">
+        <v>142</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="0"/>
+        <v>200</v>
+      </c>
+      <c r="P38">
+        <f t="shared" si="1"/>
+        <v>58</v>
+      </c>
+      <c r="Q38">
+        <f t="shared" si="2"/>
+        <v>0.33918128654970758</v>
+      </c>
+    </row>
+    <row r="39" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D39">
+        <v>487</v>
+      </c>
+      <c r="E39" t="s">
+        <v>4</v>
+      </c>
+      <c r="F39">
+        <v>200</v>
+      </c>
+      <c r="M39">
+        <v>490</v>
+      </c>
+      <c r="N39">
+        <v>157</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="0"/>
+        <v>165</v>
+      </c>
+      <c r="P39">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Q39">
+        <f t="shared" si="2"/>
+        <v>4.9689440993788817E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D40">
+        <v>490</v>
+      </c>
+      <c r="E40" t="s">
+        <v>4</v>
+      </c>
+      <c r="F40">
+        <v>165</v>
+      </c>
+      <c r="M40">
+        <v>495</v>
+      </c>
+      <c r="N40">
+        <v>192</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="0"/>
+        <v>171</v>
+      </c>
+      <c r="P40">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="Q40">
+        <f t="shared" si="2"/>
+        <v>0.11570247933884298</v>
+      </c>
+    </row>
+    <row r="41" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D41">
+        <v>495</v>
+      </c>
+      <c r="E41" t="s">
+        <v>4</v>
+      </c>
+      <c r="F41">
+        <v>171</v>
+      </c>
+      <c r="M41">
+        <v>499</v>
+      </c>
+      <c r="N41">
+        <v>153</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="0"/>
+        <v>197</v>
+      </c>
+      <c r="P41">
+        <f t="shared" si="1"/>
+        <v>44</v>
+      </c>
+      <c r="Q41">
+        <f t="shared" si="2"/>
+        <v>0.25142857142857145</v>
+      </c>
+    </row>
+    <row r="42" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D42">
+        <v>499</v>
+      </c>
+      <c r="E42" t="s">
+        <v>4</v>
+      </c>
+      <c r="F42">
+        <v>197</v>
+      </c>
+      <c r="M42">
+        <v>503</v>
+      </c>
+      <c r="N42">
+        <v>160</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="0"/>
+        <v>172</v>
+      </c>
+      <c r="P42">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q42">
+        <f t="shared" si="2"/>
+        <v>7.2289156626506021E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D43">
+        <v>503</v>
+      </c>
+      <c r="E43" t="s">
+        <v>4</v>
+      </c>
+      <c r="F43">
+        <v>172</v>
+      </c>
+      <c r="M43">
+        <v>506</v>
+      </c>
+      <c r="N43">
+        <v>170</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="0"/>
+        <v>179</v>
+      </c>
+      <c r="P43">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="Q43">
+        <f t="shared" si="2"/>
+        <v>5.1575931232091692E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D44">
+        <v>506</v>
+      </c>
+      <c r="E44" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44">
+        <v>179</v>
+      </c>
+      <c r="M44">
+        <v>509</v>
+      </c>
+      <c r="N44">
+        <v>119</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="0"/>
+        <v>115</v>
+      </c>
+      <c r="P44">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Q44">
+        <f t="shared" si="2"/>
+        <v>3.4188034188034191E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D45">
+        <v>509</v>
+      </c>
+      <c r="E45" t="s">
+        <v>4</v>
+      </c>
+      <c r="F45">
+        <v>115</v>
+      </c>
+      <c r="M45">
+        <v>512</v>
+      </c>
+      <c r="N45">
+        <v>150</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="0"/>
+        <v>166</v>
+      </c>
+      <c r="P45">
+        <f t="shared" si="1"/>
+        <v>16</v>
+      </c>
+      <c r="Q45">
+        <f t="shared" si="2"/>
+        <v>0.10126582278481013</v>
+      </c>
+    </row>
+    <row r="46" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D46">
+        <v>512</v>
+      </c>
+      <c r="E46" t="s">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>166</v>
+      </c>
+      <c r="M46">
+        <v>515</v>
+      </c>
+      <c r="N46">
+        <v>135</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="0"/>
+        <v>158</v>
+      </c>
+      <c r="P46">
+        <f t="shared" si="1"/>
+        <v>23</v>
+      </c>
+      <c r="Q46">
+        <f t="shared" si="2"/>
+        <v>0.15699658703071673</v>
+      </c>
+    </row>
+    <row r="47" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D47">
+        <v>515</v>
+      </c>
+      <c r="E47" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47">
+        <v>158</v>
+      </c>
+      <c r="M47">
+        <v>518</v>
+      </c>
+      <c r="N47">
+        <v>166</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="0"/>
+        <v>167</v>
+      </c>
+      <c r="P47">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <f t="shared" si="2"/>
+        <v>6.006006006006006E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D48">
+        <v>518</v>
+      </c>
+      <c r="E48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>167</v>
+      </c>
+      <c r="M48">
+        <v>521</v>
+      </c>
+      <c r="N48">
+        <v>190</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="0"/>
+        <v>219</v>
+      </c>
+      <c r="P48">
+        <f t="shared" si="1"/>
+        <v>29</v>
+      </c>
+      <c r="Q48">
+        <f t="shared" si="2"/>
+        <v>0.14180929095354522</v>
+      </c>
+    </row>
+    <row r="49" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D49">
+        <v>521</v>
+      </c>
+      <c r="E49" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49">
+        <v>219</v>
+      </c>
+      <c r="M49">
+        <v>525</v>
+      </c>
+      <c r="N49">
+        <v>134</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="0"/>
+        <v>154</v>
+      </c>
+      <c r="P49">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="Q49">
+        <f t="shared" si="2"/>
+        <v>0.1388888888888889</v>
+      </c>
+    </row>
+    <row r="50" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D50">
+        <v>525</v>
+      </c>
+      <c r="E50" t="s">
+        <v>4</v>
+      </c>
+      <c r="F50">
+        <v>154</v>
+      </c>
+      <c r="M50">
+        <v>529</v>
+      </c>
+      <c r="N50">
+        <v>105</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="0"/>
+        <v>143</v>
+      </c>
+      <c r="P50">
+        <f t="shared" si="1"/>
+        <v>38</v>
+      </c>
+      <c r="Q50">
+        <f t="shared" si="2"/>
+        <v>0.30645161290322581</v>
+      </c>
+    </row>
+    <row r="51" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D51">
+        <v>529</v>
+      </c>
+      <c r="E51" t="s">
+        <v>4</v>
+      </c>
+      <c r="F51">
+        <v>143</v>
+      </c>
+      <c r="M51">
+        <v>533</v>
+      </c>
+      <c r="N51">
+        <v>117</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="P51">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <f t="shared" si="2"/>
+        <v>8.5106382978723406E-3</v>
+      </c>
+    </row>
+    <row r="52" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D52">
+        <v>533</v>
+      </c>
+      <c r="E52" t="s">
+        <v>4</v>
+      </c>
+      <c r="F52">
+        <v>118</v>
+      </c>
+      <c r="M52">
+        <v>536</v>
+      </c>
+      <c r="N52">
+        <v>115</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="0"/>
+        <v>125</v>
+      </c>
+      <c r="P52">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="Q52">
+        <f t="shared" si="2"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D53">
+        <v>536</v>
+      </c>
+      <c r="E53" t="s">
+        <v>4</v>
+      </c>
+      <c r="F53">
+        <v>125</v>
+      </c>
+      <c r="M53">
+        <v>545</v>
+      </c>
+      <c r="N53">
+        <v>8</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="P53">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Q53">
+        <f t="shared" si="2"/>
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="54" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D54">
+        <v>545</v>
+      </c>
+      <c r="E54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="M54">
+        <v>547</v>
+      </c>
+      <c r="N54">
+        <v>11</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P54">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+      <c r="Q54">
+        <f t="shared" si="2"/>
+        <v>0.74285714285714288</v>
+      </c>
+    </row>
+    <row r="55" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D55">
+        <v>547</v>
+      </c>
+      <c r="E55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>24</v>
+      </c>
+      <c r="M55">
+        <v>550</v>
+      </c>
+      <c r="N55">
+        <v>10</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="P55">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Q55">
+        <f t="shared" si="2"/>
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="56" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D56">
+        <v>550</v>
+      </c>
+      <c r="E56" t="s">
+        <v>4</v>
+      </c>
+      <c r="F56">
+        <v>18</v>
+      </c>
+      <c r="M56">
+        <v>553</v>
+      </c>
+      <c r="N56">
+        <v>19</v>
+      </c>
+      <c r="O56">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P56">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Q56">
+        <f t="shared" si="2"/>
+        <v>0.23255813953488372</v>
+      </c>
+    </row>
+    <row r="57" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D57">
+        <v>553</v>
+      </c>
+      <c r="E57" t="s">
+        <v>4</v>
+      </c>
+      <c r="F57">
+        <v>24</v>
+      </c>
+      <c r="M57">
+        <v>556</v>
+      </c>
+      <c r="N57">
+        <v>32</v>
+      </c>
+      <c r="O57">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="P57">
+        <f t="shared" si="1"/>
+        <v>7</v>
+      </c>
+      <c r="Q57">
+        <f t="shared" si="2"/>
+        <v>0.19718309859154928</v>
+      </c>
+    </row>
+    <row r="58" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D58">
+        <v>556</v>
+      </c>
+      <c r="E58" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58">
+        <v>39</v>
+      </c>
+      <c r="M58">
+        <v>558</v>
+      </c>
+      <c r="N58">
+        <v>27</v>
+      </c>
+      <c r="O58">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+      <c r="P58">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q58">
+        <f t="shared" si="2"/>
+        <v>0.36363636363636365</v>
+      </c>
+    </row>
+    <row r="59" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D59">
+        <v>558</v>
+      </c>
+      <c r="E59" t="s">
+        <v>4</v>
+      </c>
+      <c r="F59">
+        <v>39</v>
+      </c>
+      <c r="M59">
+        <v>561</v>
+      </c>
+      <c r="N59">
+        <v>26</v>
+      </c>
+      <c r="O59">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="P59">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="Q59">
+        <f t="shared" si="2"/>
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="60" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D60">
+        <v>561</v>
+      </c>
+      <c r="E60" t="s">
+        <v>4</v>
+      </c>
+      <c r="F60">
+        <v>38</v>
+      </c>
+      <c r="M60">
+        <v>564</v>
+      </c>
+      <c r="N60">
+        <v>20</v>
+      </c>
+      <c r="O60">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Q60">
+        <f t="shared" si="2"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="61" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D61">
+        <v>564</v>
+      </c>
+      <c r="E61" t="s">
+        <v>4</v>
+      </c>
+      <c r="F61">
+        <v>24</v>
+      </c>
+      <c r="M61">
+        <v>567</v>
+      </c>
+      <c r="N61">
+        <v>7</v>
+      </c>
+      <c r="O61">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="P61">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="Q61">
+        <f t="shared" si="2"/>
+        <v>0.72727272727272729</v>
+      </c>
+    </row>
+    <row r="62" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D62">
+        <v>567</v>
+      </c>
+      <c r="E62" t="s">
+        <v>4</v>
+      </c>
+      <c r="F62">
+        <v>15</v>
+      </c>
+      <c r="M62">
+        <v>569</v>
+      </c>
+      <c r="N62">
+        <v>10</v>
+      </c>
+      <c r="O62">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="P62">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Q62">
+        <f t="shared" si="2"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="63" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D63">
+        <v>569</v>
+      </c>
+      <c r="E63" t="s">
+        <v>4</v>
+      </c>
+      <c r="F63">
+        <v>15</v>
+      </c>
+      <c r="M63">
+        <v>572</v>
+      </c>
+      <c r="N63">
+        <v>31</v>
+      </c>
+      <c r="O63">
+        <f t="shared" si="0"/>
+        <v>33</v>
+      </c>
+      <c r="P63">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Q63">
+        <f t="shared" si="2"/>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D64">
+        <v>572</v>
+      </c>
+      <c r="E64" t="s">
+        <v>4</v>
+      </c>
+      <c r="F64">
+        <v>33</v>
+      </c>
+      <c r="M64">
+        <v>574</v>
+      </c>
+      <c r="N64">
+        <v>21</v>
+      </c>
+      <c r="O64">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <f t="shared" si="2"/>
+        <v>4.6511627906976744E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D65">
+        <v>574</v>
+      </c>
+      <c r="E65" t="s">
+        <v>4</v>
+      </c>
+      <c r="F65">
+        <v>22</v>
+      </c>
+      <c r="M65">
+        <v>576</v>
+      </c>
+      <c r="N65">
+        <v>11</v>
+      </c>
+      <c r="O65">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Q65">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="66" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D66">
+        <v>576</v>
+      </c>
+      <c r="E66" t="s">
+        <v>4</v>
+      </c>
+      <c r="F66">
+        <v>9</v>
+      </c>
+      <c r="M66">
+        <v>577</v>
+      </c>
+      <c r="N66">
+        <v>14</v>
+      </c>
+      <c r="O66">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q66">
+        <f t="shared" si="2"/>
+        <v>6.8965517241379309E-2</v>
+      </c>
+    </row>
+    <row r="67" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D67">
+        <v>577</v>
+      </c>
+      <c r="E67" t="s">
+        <v>4</v>
+      </c>
+      <c r="F67">
+        <v>15</v>
+      </c>
+      <c r="M67">
+        <v>580</v>
+      </c>
+      <c r="N67">
+        <v>21</v>
+      </c>
+      <c r="O67">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="P67">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q67">
+        <f t="shared" si="2"/>
+        <v>4.878048780487805E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D68">
+        <v>580</v>
+      </c>
+      <c r="E68" t="s">
+        <v>4</v>
+      </c>
+      <c r="F68">
+        <v>20</v>
+      </c>
+      <c r="M68">
+        <v>584</v>
+      </c>
+      <c r="N68">
+        <v>23</v>
+      </c>
+      <c r="O68">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="P68">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="Q68">
+        <f t="shared" si="2"/>
+        <v>0.19607843137254902</v>
+      </c>
+    </row>
+    <row r="69" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D69">
+        <v>584</v>
+      </c>
+      <c r="E69" t="s">
+        <v>4</v>
+      </c>
+      <c r="F69">
+        <v>28</v>
+      </c>
+      <c r="M69">
+        <v>586</v>
+      </c>
+      <c r="N69">
+        <v>17</v>
+      </c>
+      <c r="O69">
+        <f t="shared" ref="O69:O118" si="3">VLOOKUP(M69,$D$2:$F$119,3,FALSE)</f>
+        <v>19</v>
+      </c>
+      <c r="P69">
+        <f t="shared" ref="P69:P118" si="4">ABS(N69-O69)</f>
+        <v>2</v>
+      </c>
+      <c r="Q69">
+        <f t="shared" ref="Q69:Q118" si="5">P69/(N69+O69)*2</f>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="70" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D70">
+        <v>586</v>
+      </c>
+      <c r="E70" t="s">
+        <v>4</v>
+      </c>
+      <c r="F70">
+        <v>19</v>
+      </c>
+      <c r="M70">
+        <v>587</v>
+      </c>
+      <c r="N70">
+        <v>3</v>
+      </c>
+      <c r="O70">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="P70">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q70">
+        <f t="shared" si="5"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D71">
+        <v>587</v>
+      </c>
+      <c r="E71" t="s">
+        <v>4</v>
+      </c>
+      <c r="F71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>589</v>
+      </c>
+      <c r="N71">
+        <v>22</v>
+      </c>
+      <c r="O71">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="P71">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q71">
+        <f t="shared" si="5"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D72">
+        <v>589</v>
+      </c>
+      <c r="E72" t="s">
+        <v>4</v>
+      </c>
+      <c r="F72">
+        <v>20</v>
+      </c>
+      <c r="M72">
+        <v>592</v>
+      </c>
+      <c r="N72">
+        <v>11</v>
+      </c>
+      <c r="O72">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="P72">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q72">
+        <f t="shared" si="5"/>
+        <v>0.42857142857142855</v>
+      </c>
+    </row>
+    <row r="73" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D73">
+        <v>592</v>
+      </c>
+      <c r="E73" t="s">
+        <v>4</v>
+      </c>
+      <c r="F73">
+        <v>17</v>
+      </c>
+      <c r="M73">
+        <v>594</v>
+      </c>
+      <c r="N73">
+        <v>12</v>
+      </c>
+      <c r="O73">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="P73">
+        <f t="shared" si="4"/>
+        <v>11</v>
+      </c>
+      <c r="Q73">
+        <f t="shared" si="5"/>
+        <v>0.62857142857142856</v>
+      </c>
+    </row>
+    <row r="74" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D74">
+        <v>594</v>
+      </c>
+      <c r="E74" t="s">
+        <v>4</v>
+      </c>
+      <c r="F74">
+        <v>23</v>
+      </c>
+      <c r="M74">
+        <v>596</v>
+      </c>
+      <c r="N74">
+        <v>17</v>
+      </c>
+      <c r="O74">
+        <f t="shared" si="3"/>
+        <v>17</v>
+      </c>
+      <c r="P74">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D75">
+        <v>596</v>
+      </c>
+      <c r="E75" t="s">
+        <v>4</v>
+      </c>
+      <c r="F75">
+        <v>17</v>
+      </c>
+      <c r="M75">
+        <v>598</v>
+      </c>
+      <c r="N75">
+        <v>12</v>
+      </c>
+      <c r="O75">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="P75">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Q75">
+        <f t="shared" si="5"/>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="76" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D76">
+        <v>598</v>
+      </c>
+      <c r="E76" t="s">
+        <v>4</v>
+      </c>
+      <c r="F76">
+        <v>16</v>
+      </c>
+      <c r="M76">
+        <v>601</v>
+      </c>
+      <c r="N76">
+        <v>31</v>
+      </c>
+      <c r="O76">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="P76">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q76">
+        <f t="shared" si="5"/>
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D77">
+        <v>601</v>
+      </c>
+      <c r="E77" t="s">
+        <v>4</v>
+      </c>
+      <c r="F77">
+        <v>30</v>
+      </c>
+      <c r="M77">
+        <v>603</v>
+      </c>
+      <c r="N77">
+        <v>19</v>
+      </c>
+      <c r="O77">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="P77">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q77">
+        <f t="shared" si="5"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D78">
+        <v>603</v>
+      </c>
+      <c r="E78" t="s">
+        <v>4</v>
+      </c>
+      <c r="F78">
+        <v>20</v>
+      </c>
+      <c r="M78">
+        <v>606</v>
+      </c>
+      <c r="N78">
+        <v>49</v>
+      </c>
+      <c r="O78">
+        <f t="shared" si="3"/>
+        <v>49</v>
+      </c>
+      <c r="P78">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D79">
+        <v>606</v>
+      </c>
+      <c r="E79" t="s">
+        <v>4</v>
+      </c>
+      <c r="F79">
+        <v>49</v>
+      </c>
+      <c r="M79">
+        <v>609</v>
+      </c>
+      <c r="N79">
+        <v>40</v>
+      </c>
+      <c r="O79">
+        <f t="shared" si="3"/>
+        <v>44</v>
+      </c>
+      <c r="P79">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Q79">
+        <f t="shared" si="5"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D80">
+        <v>609</v>
+      </c>
+      <c r="E80" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80">
+        <v>44</v>
+      </c>
+      <c r="M80">
+        <v>612</v>
+      </c>
+      <c r="N80">
+        <v>28</v>
+      </c>
+      <c r="O80">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="P80">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q80">
+        <f t="shared" si="5"/>
+        <v>0.11320754716981132</v>
+      </c>
+    </row>
+    <row r="81" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D81">
+        <v>612</v>
+      </c>
+      <c r="E81" t="s">
+        <v>4</v>
+      </c>
+      <c r="F81">
+        <v>25</v>
+      </c>
+      <c r="M81">
+        <v>615</v>
+      </c>
+      <c r="N81">
+        <v>37</v>
+      </c>
+      <c r="O81">
+        <f t="shared" si="3"/>
+        <v>42</v>
+      </c>
+      <c r="P81">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="Q81">
+        <f t="shared" si="5"/>
+        <v>0.12658227848101267</v>
+      </c>
+    </row>
+    <row r="82" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D82">
+        <v>615</v>
+      </c>
+      <c r="E82" t="s">
+        <v>4</v>
+      </c>
+      <c r="F82">
+        <v>42</v>
+      </c>
+      <c r="M82">
+        <v>618</v>
+      </c>
+      <c r="N82">
+        <v>21</v>
+      </c>
+      <c r="O82">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="P82">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q82">
+        <f t="shared" si="5"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="83" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D83">
+        <v>618</v>
+      </c>
+      <c r="E83" t="s">
+        <v>4</v>
+      </c>
+      <c r="F83">
+        <v>24</v>
+      </c>
+      <c r="M83">
+        <v>621</v>
+      </c>
+      <c r="N83">
+        <v>25</v>
+      </c>
+      <c r="O83">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="P83">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D84">
+        <v>621</v>
+      </c>
+      <c r="E84" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84">
+        <v>25</v>
+      </c>
+      <c r="M84">
+        <v>624</v>
+      </c>
+      <c r="N84">
+        <v>23</v>
+      </c>
+      <c r="O84">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="P84">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q84">
+        <f t="shared" si="5"/>
+        <v>0.13953488372093023</v>
+      </c>
+    </row>
+    <row r="85" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D85">
+        <v>624</v>
+      </c>
+      <c r="E85" t="s">
+        <v>4</v>
+      </c>
+      <c r="F85">
+        <v>20</v>
+      </c>
+      <c r="M85">
+        <v>627</v>
+      </c>
+      <c r="N85">
+        <v>17</v>
+      </c>
+      <c r="O85">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="P85">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q85">
+        <f t="shared" si="5"/>
+        <v>6.0606060606060608E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D86">
+        <v>627</v>
+      </c>
+      <c r="E86" t="s">
+        <v>4</v>
+      </c>
+      <c r="F86">
+        <v>16</v>
+      </c>
+      <c r="M86">
+        <v>628</v>
+      </c>
+      <c r="N86">
+        <v>4</v>
+      </c>
+      <c r="O86">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="P86">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q86">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="87" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D87">
+        <v>628</v>
+      </c>
+      <c r="E87" t="s">
+        <v>4</v>
+      </c>
+      <c r="F87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>633</v>
+      </c>
+      <c r="N87">
+        <v>10</v>
+      </c>
+      <c r="O87">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="P87">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q87">
+        <f t="shared" si="5"/>
+        <v>0.46153846153846156</v>
+      </c>
+    </row>
+    <row r="88" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D88">
+        <v>633</v>
+      </c>
+      <c r="E88" t="s">
+        <v>4</v>
+      </c>
+      <c r="F88">
+        <v>16</v>
+      </c>
+      <c r="M88">
+        <v>637</v>
+      </c>
+      <c r="N88">
+        <v>4</v>
+      </c>
+      <c r="O88">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="P88">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Q88">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="89" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D89">
+        <v>637</v>
+      </c>
+      <c r="E89" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89">
+        <v>8</v>
+      </c>
+      <c r="M89">
+        <v>640</v>
+      </c>
+      <c r="N89">
+        <v>6</v>
+      </c>
+      <c r="O89">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="P89">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <f t="shared" si="5"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="90" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D90">
+        <v>640</v>
+      </c>
+      <c r="E90" t="s">
+        <v>4</v>
+      </c>
+      <c r="F90">
+        <v>7</v>
+      </c>
+      <c r="M90">
+        <v>645</v>
+      </c>
+      <c r="N90">
+        <v>20</v>
+      </c>
+      <c r="O90">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="P90">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D91">
+        <v>645</v>
+      </c>
+      <c r="E91" t="s">
+        <v>4</v>
+      </c>
+      <c r="F91">
+        <v>20</v>
+      </c>
+      <c r="M91">
+        <v>648</v>
+      </c>
+      <c r="N91">
+        <v>20</v>
+      </c>
+      <c r="O91">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="P91">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q91">
+        <f t="shared" si="5"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D92">
+        <v>648</v>
+      </c>
+      <c r="E92" t="s">
+        <v>4</v>
+      </c>
+      <c r="F92">
+        <v>22</v>
+      </c>
+      <c r="M92">
+        <v>651</v>
+      </c>
+      <c r="N92">
+        <v>6</v>
+      </c>
+      <c r="O92">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P92">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q92">
+        <f t="shared" si="5"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="93" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D93">
+        <v>651</v>
+      </c>
+      <c r="E93" t="s">
+        <v>4</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="M93">
+        <v>655</v>
+      </c>
+      <c r="N93">
+        <v>9</v>
+      </c>
+      <c r="O93">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="P93">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q93">
+        <f t="shared" si="5"/>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="94" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D94">
+        <v>655</v>
+      </c>
+      <c r="E94" t="s">
+        <v>4</v>
+      </c>
+      <c r="F94">
+        <v>12</v>
+      </c>
+      <c r="M94">
+        <v>661</v>
+      </c>
+      <c r="N94">
+        <v>13</v>
+      </c>
+      <c r="O94">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="P94">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q94">
+        <f t="shared" si="5"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="95" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D95">
+        <v>661</v>
+      </c>
+      <c r="E95" t="s">
+        <v>4</v>
+      </c>
+      <c r="F95">
+        <v>15</v>
+      </c>
+      <c r="M95">
+        <v>664</v>
+      </c>
+      <c r="N95">
+        <v>12</v>
+      </c>
+      <c r="O95">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="P95">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q95">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="96" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D96">
+        <v>664</v>
+      </c>
+      <c r="E96" t="s">
+        <v>4</v>
+      </c>
+      <c r="F96">
+        <v>13</v>
+      </c>
+      <c r="M96">
+        <v>669</v>
+      </c>
+      <c r="N96">
+        <v>15</v>
+      </c>
+      <c r="O96">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="P96">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D97">
+        <v>669</v>
+      </c>
+      <c r="E97" t="s">
+        <v>4</v>
+      </c>
+      <c r="F97">
+        <v>15</v>
+      </c>
+      <c r="M97">
+        <v>672</v>
+      </c>
+      <c r="N97">
+        <v>8</v>
+      </c>
+      <c r="O97">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="P97">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q97">
+        <f t="shared" si="5"/>
+        <v>0.46153846153846156</v>
+      </c>
+    </row>
+    <row r="98" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D98">
+        <v>672</v>
+      </c>
+      <c r="E98" t="s">
+        <v>4</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+      <c r="M98">
+        <v>676</v>
+      </c>
+      <c r="N98">
+        <v>14</v>
+      </c>
+      <c r="O98">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="P98">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D99">
+        <v>676</v>
+      </c>
+      <c r="E99" t="s">
+        <v>4</v>
+      </c>
+      <c r="F99">
+        <v>14</v>
+      </c>
+      <c r="M99">
+        <v>678</v>
+      </c>
+      <c r="N99">
+        <v>15</v>
+      </c>
+      <c r="O99">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="P99">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q99">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D100">
+        <v>678</v>
+      </c>
+      <c r="E100" t="s">
+        <v>4</v>
+      </c>
+      <c r="F100">
+        <v>15</v>
+      </c>
+      <c r="M100">
+        <v>681</v>
+      </c>
+      <c r="N100">
+        <v>25</v>
+      </c>
+      <c r="O100">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="P100">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q100">
+        <f t="shared" si="5"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D101">
+        <v>681</v>
+      </c>
+      <c r="E101" t="s">
+        <v>4</v>
+      </c>
+      <c r="F101">
+        <v>24</v>
+      </c>
+      <c r="M101">
+        <v>684</v>
+      </c>
+      <c r="N101">
+        <v>31</v>
+      </c>
+      <c r="O101">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="P101">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q101">
+        <f t="shared" si="5"/>
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D102">
+        <v>684</v>
+      </c>
+      <c r="E102" t="s">
+        <v>4</v>
+      </c>
+      <c r="F102">
+        <v>30</v>
+      </c>
+      <c r="M102">
+        <v>689</v>
+      </c>
+      <c r="N102">
+        <v>19</v>
+      </c>
+      <c r="O102">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="P102">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q102">
+        <f t="shared" si="5"/>
+        <v>0.27272727272727271</v>
+      </c>
+    </row>
+    <row r="103" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D103">
+        <v>689</v>
+      </c>
+      <c r="E103" t="s">
+        <v>4</v>
+      </c>
+      <c r="F103">
+        <v>25</v>
+      </c>
+      <c r="M103">
+        <v>693</v>
+      </c>
+      <c r="N103">
+        <v>24</v>
+      </c>
+      <c r="O103">
+        <f t="shared" si="3"/>
+        <v>24</v>
+      </c>
+      <c r="P103">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D104">
+        <v>693</v>
+      </c>
+      <c r="E104" t="s">
+        <v>4</v>
+      </c>
+      <c r="F104">
+        <v>24</v>
+      </c>
+      <c r="M104">
+        <v>696</v>
+      </c>
+      <c r="N104">
+        <v>20</v>
+      </c>
+      <c r="O104">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="P104">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D105">
+        <v>696</v>
+      </c>
+      <c r="E105" t="s">
+        <v>4</v>
+      </c>
+      <c r="F105">
+        <v>20</v>
+      </c>
+      <c r="M105">
+        <v>699</v>
+      </c>
+      <c r="N105">
+        <v>12</v>
+      </c>
+      <c r="O105">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="P105">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q105">
+        <f t="shared" si="5"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="106" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D106">
+        <v>699</v>
+      </c>
+      <c r="E106" t="s">
+        <v>4</v>
+      </c>
+      <c r="F106">
+        <v>13</v>
+      </c>
+      <c r="M106">
+        <v>702</v>
+      </c>
+      <c r="N106">
+        <v>4</v>
+      </c>
+      <c r="O106">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="P106">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="Q106">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="107" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D107">
+        <v>702</v>
+      </c>
+      <c r="E107" t="s">
+        <v>4</v>
+      </c>
+      <c r="F107">
+        <v>8</v>
+      </c>
+      <c r="M107">
+        <v>705</v>
+      </c>
+      <c r="N107">
+        <v>16</v>
+      </c>
+      <c r="O107">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="P107">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q107">
+        <f t="shared" si="5"/>
+        <v>6.4516129032258063E-2</v>
+      </c>
+    </row>
+    <row r="108" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D108">
+        <v>705</v>
+      </c>
+      <c r="E108" t="s">
+        <v>4</v>
+      </c>
+      <c r="F108">
+        <v>15</v>
+      </c>
+      <c r="M108">
+        <v>709</v>
+      </c>
+      <c r="N108">
+        <v>18</v>
+      </c>
+      <c r="O108">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="P108">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q108">
+        <f t="shared" si="5"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
+    </row>
+    <row r="109" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D109">
+        <v>709</v>
+      </c>
+      <c r="E109" t="s">
+        <v>4</v>
+      </c>
+      <c r="F109">
+        <v>19</v>
+      </c>
+      <c r="M109">
+        <v>712</v>
+      </c>
+      <c r="N109">
+        <v>2</v>
+      </c>
+      <c r="O109">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="P109">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q109">
+        <f t="shared" si="5"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="110" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D110">
+        <v>712</v>
+      </c>
+      <c r="E110" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110">
+        <v>4</v>
+      </c>
+      <c r="M110">
+        <v>716</v>
+      </c>
+      <c r="N110">
+        <v>15</v>
+      </c>
+      <c r="O110">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="P110">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="Q110">
+        <f t="shared" si="5"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="111" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D111">
+        <v>716</v>
+      </c>
+      <c r="E111" t="s">
+        <v>4</v>
+      </c>
+      <c r="F111">
+        <v>21</v>
+      </c>
+      <c r="M111">
+        <v>718</v>
+      </c>
+      <c r="N111">
+        <v>23</v>
+      </c>
+      <c r="O111">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="P111">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q111">
+        <f t="shared" si="5"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+    </row>
+    <row r="112" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D112">
+        <v>718</v>
+      </c>
+      <c r="E112" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112">
+        <v>21</v>
+      </c>
+      <c r="M112">
+        <v>721</v>
+      </c>
+      <c r="N112">
+        <v>16</v>
+      </c>
+      <c r="O112">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="P112">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="Q112">
+        <f t="shared" si="5"/>
+        <v>0.17142857142857143</v>
+      </c>
+    </row>
+    <row r="113" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D113">
+        <v>721</v>
+      </c>
+      <c r="E113" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113">
+        <v>19</v>
+      </c>
+      <c r="M113">
+        <v>723</v>
+      </c>
+      <c r="N113">
+        <v>26</v>
+      </c>
+      <c r="O113">
+        <f t="shared" si="3"/>
+        <v>19</v>
+      </c>
+      <c r="P113">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="Q113">
+        <f t="shared" si="5"/>
+        <v>0.31111111111111112</v>
+      </c>
+    </row>
+    <row r="114" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D114">
+        <v>723</v>
+      </c>
+      <c r="E114" t="s">
+        <v>4</v>
+      </c>
+      <c r="F114">
+        <v>19</v>
+      </c>
+      <c r="M114">
+        <v>725</v>
+      </c>
+      <c r="N114">
+        <v>18</v>
+      </c>
+      <c r="O114">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="P114">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="Q114">
+        <f t="shared" si="5"/>
+        <v>0.32258064516129031</v>
+      </c>
+    </row>
+    <row r="115" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D115">
+        <v>725</v>
+      </c>
+      <c r="E115" t="s">
+        <v>4</v>
+      </c>
+      <c r="F115">
+        <v>13</v>
+      </c>
+      <c r="M115">
+        <v>728</v>
+      </c>
+      <c r="N115">
+        <v>18</v>
+      </c>
+      <c r="O115">
+        <f t="shared" si="3"/>
+        <v>23</v>
+      </c>
+      <c r="P115">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="Q115">
+        <f t="shared" si="5"/>
+        <v>0.24390243902439024</v>
+      </c>
+    </row>
+    <row r="116" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D116">
+        <v>728</v>
+      </c>
+      <c r="E116" t="s">
+        <v>4</v>
+      </c>
+      <c r="F116">
+        <v>23</v>
+      </c>
+      <c r="M116">
+        <v>731</v>
+      </c>
+      <c r="N116">
+        <v>6</v>
+      </c>
+      <c r="O116">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="P116">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q116">
+        <f t="shared" si="5"/>
+        <v>0.15384615384615385</v>
+      </c>
+    </row>
+    <row r="117" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D117">
+        <v>731</v>
+      </c>
+      <c r="E117" t="s">
+        <v>4</v>
+      </c>
+      <c r="F117">
+        <v>7</v>
+      </c>
+      <c r="M117">
+        <v>734</v>
+      </c>
+      <c r="N117">
+        <v>7</v>
+      </c>
+      <c r="O117">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="P117">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="Q117">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="D118">
+        <v>734</v>
+      </c>
+      <c r="E118" t="s">
+        <v>4</v>
+      </c>
+      <c r="F118">
+        <v>7</v>
+      </c>
+      <c r="M118">
+        <v>738</v>
+      </c>
+      <c r="N118">
+        <v>11</v>
+      </c>
+      <c r="O118">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="P118">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="Q118">
+        <f t="shared" si="5"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="119" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="D119">
+        <v>738</v>
+      </c>
+      <c r="E119" t="s">
+        <v>4</v>
+      </c>
+      <c r="F119">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="M3:Q118" xr:uid="{FBA55525-5725-432D-8CC7-0A0B7E5373EF}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="0.724637681"/>
+        <filter val="0.727272727"/>
+        <filter val="0.742857143"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Estimacion_error/datos_aves_marinas/2025/abril/Rompeolas/conteos_reales.xlsx
+++ b/Estimacion_error/datos_aves_marinas/2025/abril/Rompeolas/conteos_reales.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Data_Saiensss\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2025\abril\Rompeolas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Renzo\Desktop\Estadística\Trabajos (laborales)\BMAP\Proyectos\conteo-aves-bmap\Estimacion_error\datos_aves_marinas\2025\abril\Rompeolas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97593A8A-1E53-4323-9502-928073946047}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00D10443-CC24-4362-8D13-8CAF55853960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$M$3:$Q$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Hoja1!$L$3:$S$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$340</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -31,15 +31,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="31">
   <si>
     <t>FOTO</t>
   </si>
@@ -102,6 +99,36 @@
   </si>
   <si>
     <t>sMAPE</t>
+  </si>
+  <si>
+    <t>x_0.48</t>
+  </si>
+  <si>
+    <t>Sin sahi</t>
+  </si>
+  <si>
+    <t>Error_sahi</t>
+  </si>
+  <si>
+    <t>Con sahi</t>
+  </si>
+  <si>
+    <t>SMAPE</t>
+  </si>
+  <si>
+    <t>smape_sahi</t>
+  </si>
+  <si>
+    <t>sin sahi</t>
+  </si>
+  <si>
+    <t>con sahi</t>
+  </si>
+  <si>
+    <t>sin_sahi</t>
+  </si>
+  <si>
+    <t>con_sahi</t>
   </si>
 </sst>
 </file>
@@ -178,9 +205,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -218,9 +245,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -253,26 +280,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -305,26 +315,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -500,12 +493,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:C340"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -516,7 +509,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>222</v>
       </c>
@@ -527,7 +520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>222</v>
       </c>
@@ -538,7 +531,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>362</v>
       </c>
@@ -549,7 +542,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>371</v>
       </c>
@@ -560,7 +553,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>378</v>
       </c>
@@ -571,7 +564,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>380</v>
       </c>
@@ -582,7 +575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>380</v>
       </c>
@@ -593,7 +586,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>380</v>
       </c>
@@ -604,7 +597,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>384</v>
       </c>
@@ -615,7 +608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>384</v>
       </c>
@@ -626,7 +619,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>384</v>
       </c>
@@ -637,7 +630,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>384</v>
       </c>
@@ -648,7 +641,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>389</v>
       </c>
@@ -659,7 +652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>389</v>
       </c>
@@ -670,7 +663,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>389</v>
       </c>
@@ -681,7 +674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>392</v>
       </c>
@@ -692,7 +685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>393</v>
       </c>
@@ -703,7 +696,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>393</v>
       </c>
@@ -714,7 +707,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>397</v>
       </c>
@@ -725,7 +718,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>397</v>
       </c>
@@ -736,7 +729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>397</v>
       </c>
@@ -747,7 +740,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>397</v>
       </c>
@@ -758,7 +751,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>397</v>
       </c>
@@ -769,7 +762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>402</v>
       </c>
@@ -780,7 +773,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>402</v>
       </c>
@@ -791,7 +784,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>402</v>
       </c>
@@ -802,7 +795,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>402</v>
       </c>
@@ -813,7 +806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>402</v>
       </c>
@@ -824,7 +817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>405</v>
       </c>
@@ -835,7 +828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>405</v>
       </c>
@@ -846,7 +839,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>405</v>
       </c>
@@ -857,7 +850,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>405</v>
       </c>
@@ -868,7 +861,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>408</v>
       </c>
@@ -879,7 +872,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>408</v>
       </c>
@@ -890,7 +883,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>408</v>
       </c>
@@ -901,7 +894,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>408</v>
       </c>
@@ -912,7 +905,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>411</v>
       </c>
@@ -923,7 +916,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>411</v>
       </c>
@@ -934,7 +927,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>416</v>
       </c>
@@ -945,7 +938,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>416</v>
       </c>
@@ -956,7 +949,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>416</v>
       </c>
@@ -967,7 +960,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>416</v>
       </c>
@@ -978,7 +971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>419</v>
       </c>
@@ -989,7 +982,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>419</v>
       </c>
@@ -1000,7 +993,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>419</v>
       </c>
@@ -1011,7 +1004,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>419</v>
       </c>
@@ -1022,7 +1015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>422</v>
       </c>
@@ -1033,7 +1026,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>422</v>
       </c>
@@ -1044,7 +1037,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>425</v>
       </c>
@@ -1055,7 +1048,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>425</v>
       </c>
@@ -1066,7 +1059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>425</v>
       </c>
@@ -1077,7 +1070,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>425</v>
       </c>
@@ -1088,7 +1081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>425</v>
       </c>
@@ -1099,7 +1092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>428</v>
       </c>
@@ -1110,7 +1103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>428</v>
       </c>
@@ -1121,7 +1114,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>428</v>
       </c>
@@ -1132,7 +1125,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>428</v>
       </c>
@@ -1143,7 +1136,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>431</v>
       </c>
@@ -1154,7 +1147,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>431</v>
       </c>
@@ -1165,7 +1158,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>431</v>
       </c>
@@ -1176,7 +1169,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>431</v>
       </c>
@@ -1187,7 +1180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>433</v>
       </c>
@@ -1198,7 +1191,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>433</v>
       </c>
@@ -1209,7 +1202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>433</v>
       </c>
@@ -1220,7 +1213,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>433</v>
       </c>
@@ -1231,7 +1224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>436</v>
       </c>
@@ -1242,7 +1235,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>436</v>
       </c>
@@ -1253,7 +1246,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>436</v>
       </c>
@@ -1264,7 +1257,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>436</v>
       </c>
@@ -1275,7 +1268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>436</v>
       </c>
@@ -1286,7 +1279,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>436</v>
       </c>
@@ -1297,7 +1290,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>440</v>
       </c>
@@ -1308,7 +1301,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>440</v>
       </c>
@@ -1319,7 +1312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>440</v>
       </c>
@@ -1330,7 +1323,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>440</v>
       </c>
@@ -1341,7 +1334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>440</v>
       </c>
@@ -1352,7 +1345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>443</v>
       </c>
@@ -1363,7 +1356,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>443</v>
       </c>
@@ -1374,7 +1367,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>443</v>
       </c>
@@ -1385,7 +1378,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>443</v>
       </c>
@@ -1396,7 +1389,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>446</v>
       </c>
@@ -1407,7 +1400,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>446</v>
       </c>
@@ -1418,7 +1411,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>446</v>
       </c>
@@ -1429,7 +1422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>446</v>
       </c>
@@ -1440,7 +1433,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>446</v>
       </c>
@@ -1451,7 +1444,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>450</v>
       </c>
@@ -1462,7 +1455,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>450</v>
       </c>
@@ -1473,7 +1466,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>450</v>
       </c>
@@ -1484,7 +1477,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>450</v>
       </c>
@@ -1495,7 +1488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>450</v>
       </c>
@@ -1506,7 +1499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>450</v>
       </c>
@@ -1517,7 +1510,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>453</v>
       </c>
@@ -1528,7 +1521,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>453</v>
       </c>
@@ -1539,7 +1532,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>453</v>
       </c>
@@ -1550,7 +1543,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>453</v>
       </c>
@@ -1561,7 +1554,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>455</v>
       </c>
@@ -1572,7 +1565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>455</v>
       </c>
@@ -1583,7 +1576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>455</v>
       </c>
@@ -1594,7 +1587,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>455</v>
       </c>
@@ -1605,7 +1598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>455</v>
       </c>
@@ -1616,7 +1609,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>455</v>
       </c>
@@ -1627,7 +1620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>458</v>
       </c>
@@ -1638,7 +1631,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>458</v>
       </c>
@@ -1649,7 +1642,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>458</v>
       </c>
@@ -1660,7 +1653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>458</v>
       </c>
@@ -1671,7 +1664,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>458</v>
       </c>
@@ -1682,7 +1675,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>461</v>
       </c>
@@ -1693,7 +1686,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>461</v>
       </c>
@@ -1704,7 +1697,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>461</v>
       </c>
@@ -1715,7 +1708,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>461</v>
       </c>
@@ -1726,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>466</v>
       </c>
@@ -1737,7 +1730,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>466</v>
       </c>
@@ -1748,7 +1741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>466</v>
       </c>
@@ -1759,7 +1752,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>466</v>
       </c>
@@ -1770,7 +1763,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>466</v>
       </c>
@@ -1781,7 +1774,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>466</v>
       </c>
@@ -1792,7 +1785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>466</v>
       </c>
@@ -1803,7 +1796,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>470</v>
       </c>
@@ -1814,7 +1807,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>470</v>
       </c>
@@ -1825,7 +1818,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>470</v>
       </c>
@@ -1836,7 +1829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>470</v>
       </c>
@@ -1847,7 +1840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>470</v>
       </c>
@@ -1858,7 +1851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>470</v>
       </c>
@@ -1869,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>473</v>
       </c>
@@ -1880,7 +1873,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>473</v>
       </c>
@@ -1891,7 +1884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>473</v>
       </c>
@@ -1902,7 +1895,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>473</v>
       </c>
@@ -1913,7 +1906,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>475</v>
       </c>
@@ -1924,7 +1917,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>475</v>
       </c>
@@ -1935,7 +1928,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>475</v>
       </c>
@@ -1946,7 +1939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>475</v>
       </c>
@@ -1957,7 +1950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>475</v>
       </c>
@@ -1968,7 +1961,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>478</v>
       </c>
@@ -1979,7 +1972,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>478</v>
       </c>
@@ -1990,7 +1983,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>478</v>
       </c>
@@ -2001,7 +1994,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>478</v>
       </c>
@@ -2012,7 +2005,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>478</v>
       </c>
@@ -2023,7 +2016,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>481</v>
       </c>
@@ -2034,7 +2027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>481</v>
       </c>
@@ -2045,7 +2038,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>481</v>
       </c>
@@ -2056,7 +2049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>481</v>
       </c>
@@ -2067,7 +2060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>484</v>
       </c>
@@ -2078,7 +2071,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>484</v>
       </c>
@@ -2089,7 +2082,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>484</v>
       </c>
@@ -2100,7 +2093,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>484</v>
       </c>
@@ -2111,7 +2104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>487</v>
       </c>
@@ -2122,7 +2115,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>487</v>
       </c>
@@ -2133,7 +2126,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>487</v>
       </c>
@@ -2144,7 +2137,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>487</v>
       </c>
@@ -2155,7 +2148,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>487</v>
       </c>
@@ -2166,7 +2159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>490</v>
       </c>
@@ -2177,7 +2170,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>490</v>
       </c>
@@ -2188,7 +2181,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>490</v>
       </c>
@@ -2199,7 +2192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>490</v>
       </c>
@@ -2210,7 +2203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>490</v>
       </c>
@@ -2221,7 +2214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>495</v>
       </c>
@@ -2232,7 +2225,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>495</v>
       </c>
@@ -2243,7 +2236,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>495</v>
       </c>
@@ -2254,7 +2247,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>495</v>
       </c>
@@ -2265,7 +2258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>495</v>
       </c>
@@ -2276,7 +2269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>495</v>
       </c>
@@ -2287,7 +2280,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>499</v>
       </c>
@@ -2298,7 +2291,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>499</v>
       </c>
@@ -2309,7 +2302,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>499</v>
       </c>
@@ -2320,7 +2313,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>499</v>
       </c>
@@ -2331,7 +2324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>499</v>
       </c>
@@ -2342,7 +2335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>499</v>
       </c>
@@ -2353,7 +2346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>503</v>
       </c>
@@ -2364,7 +2357,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>503</v>
       </c>
@@ -2375,7 +2368,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>503</v>
       </c>
@@ -2386,7 +2379,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>506</v>
       </c>
@@ -2397,7 +2390,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>506</v>
       </c>
@@ -2408,7 +2401,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>506</v>
       </c>
@@ -2419,7 +2412,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>506</v>
       </c>
@@ -2430,7 +2423,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>506</v>
       </c>
@@ -2441,7 +2434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>506</v>
       </c>
@@ -2452,7 +2445,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>509</v>
       </c>
@@ -2463,7 +2456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>509</v>
       </c>
@@ -2474,7 +2467,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>509</v>
       </c>
@@ -2485,7 +2478,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>509</v>
       </c>
@@ -2496,7 +2489,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>512</v>
       </c>
@@ -2507,7 +2500,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>512</v>
       </c>
@@ -2518,7 +2511,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>512</v>
       </c>
@@ -2529,7 +2522,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>512</v>
       </c>
@@ -2540,7 +2533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>512</v>
       </c>
@@ -2551,7 +2544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>512</v>
       </c>
@@ -2562,7 +2555,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>515</v>
       </c>
@@ -2573,7 +2566,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>515</v>
       </c>
@@ -2584,7 +2577,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>515</v>
       </c>
@@ -2595,7 +2588,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>518</v>
       </c>
@@ -2606,7 +2599,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>518</v>
       </c>
@@ -2617,7 +2610,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>518</v>
       </c>
@@ -2628,7 +2621,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>521</v>
       </c>
@@ -2639,7 +2632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>521</v>
       </c>
@@ -2650,7 +2643,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>525</v>
       </c>
@@ -2661,7 +2654,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>525</v>
       </c>
@@ -2672,7 +2665,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>529</v>
       </c>
@@ -2683,7 +2676,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>529</v>
       </c>
@@ -2694,7 +2687,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>529</v>
       </c>
@@ -2705,7 +2698,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>529</v>
       </c>
@@ -2716,7 +2709,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>529</v>
       </c>
@@ -2727,7 +2720,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>533</v>
       </c>
@@ -2738,7 +2731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>533</v>
       </c>
@@ -2749,7 +2742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>533</v>
       </c>
@@ -2760,7 +2753,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>536</v>
       </c>
@@ -2771,7 +2764,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>545</v>
       </c>
@@ -2782,7 +2775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>545</v>
       </c>
@@ -2793,7 +2786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>547</v>
       </c>
@@ -2804,7 +2797,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>547</v>
       </c>
@@ -2815,7 +2808,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>547</v>
       </c>
@@ -2826,7 +2819,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>547</v>
       </c>
@@ -2837,7 +2830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>550</v>
       </c>
@@ -2848,7 +2841,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>550</v>
       </c>
@@ -2859,7 +2852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>550</v>
       </c>
@@ -2870,7 +2863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>553</v>
       </c>
@@ -2881,7 +2874,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>553</v>
       </c>
@@ -2892,7 +2885,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>553</v>
       </c>
@@ -2903,7 +2896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>556</v>
       </c>
@@ -2914,7 +2907,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>556</v>
       </c>
@@ -2925,7 +2918,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>558</v>
       </c>
@@ -2936,7 +2929,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>561</v>
       </c>
@@ -2947,7 +2940,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>561</v>
       </c>
@@ -2958,7 +2951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>561</v>
       </c>
@@ -2969,7 +2962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>564</v>
       </c>
@@ -2980,7 +2973,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>564</v>
       </c>
@@ -2991,7 +2984,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>567</v>
       </c>
@@ -3002,7 +2995,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>567</v>
       </c>
@@ -3013,7 +3006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>569</v>
       </c>
@@ -3024,7 +3017,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>569</v>
       </c>
@@ -3035,7 +3028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>572</v>
       </c>
@@ -3046,7 +3039,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>572</v>
       </c>
@@ -3057,7 +3050,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>574</v>
       </c>
@@ -3068,7 +3061,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>574</v>
       </c>
@@ -3079,7 +3072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>576</v>
       </c>
@@ -3090,7 +3083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>576</v>
       </c>
@@ -3101,7 +3094,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>577</v>
       </c>
@@ -3112,7 +3105,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>577</v>
       </c>
@@ -3123,7 +3116,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>580</v>
       </c>
@@ -3134,7 +3127,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>580</v>
       </c>
@@ -3145,7 +3138,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>584</v>
       </c>
@@ -3156,7 +3149,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>584</v>
       </c>
@@ -3167,7 +3160,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>586</v>
       </c>
@@ -3178,7 +3171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>586</v>
       </c>
@@ -3189,7 +3182,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>587</v>
       </c>
@@ -3200,7 +3193,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>587</v>
       </c>
@@ -3211,7 +3204,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>589</v>
       </c>
@@ -3222,7 +3215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>589</v>
       </c>
@@ -3233,7 +3226,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>589</v>
       </c>
@@ -3244,7 +3237,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>592</v>
       </c>
@@ -3255,7 +3248,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>592</v>
       </c>
@@ -3266,7 +3259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>594</v>
       </c>
@@ -3277,7 +3270,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>594</v>
       </c>
@@ -3288,7 +3281,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>596</v>
       </c>
@@ -3299,7 +3292,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>596</v>
       </c>
@@ -3310,7 +3303,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>598</v>
       </c>
@@ -3321,7 +3314,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>601</v>
       </c>
@@ -3332,7 +3325,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>601</v>
       </c>
@@ -3343,7 +3336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>603</v>
       </c>
@@ -3354,7 +3347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>606</v>
       </c>
@@ -3365,7 +3358,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>606</v>
       </c>
@@ -3376,7 +3369,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>609</v>
       </c>
@@ -3387,7 +3380,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>612</v>
       </c>
@@ -3398,7 +3391,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>615</v>
       </c>
@@ -3409,7 +3402,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>618</v>
       </c>
@@ -3420,7 +3413,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>618</v>
       </c>
@@ -3431,7 +3424,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>621</v>
       </c>
@@ -3442,7 +3435,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>621</v>
       </c>
@@ -3453,7 +3446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>624</v>
       </c>
@@ -3464,7 +3457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>624</v>
       </c>
@@ -3475,7 +3468,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>624</v>
       </c>
@@ -3486,7 +3479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>627</v>
       </c>
@@ -3497,7 +3490,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>627</v>
       </c>
@@ -3508,7 +3501,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>627</v>
       </c>
@@ -3519,7 +3512,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>628</v>
       </c>
@@ -3530,7 +3523,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>628</v>
       </c>
@@ -3541,7 +3534,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>633</v>
       </c>
@@ -3552,7 +3545,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>633</v>
       </c>
@@ -3563,7 +3556,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>637</v>
       </c>
@@ -3574,7 +3567,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>637</v>
       </c>
@@ -3585,7 +3578,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>640</v>
       </c>
@@ -3596,7 +3589,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>640</v>
       </c>
@@ -3607,7 +3600,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>645</v>
       </c>
@@ -3618,7 +3611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>645</v>
       </c>
@@ -3629,7 +3622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>648</v>
       </c>
@@ -3640,7 +3633,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>648</v>
       </c>
@@ -3651,7 +3644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>648</v>
       </c>
@@ -3662,7 +3655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>651</v>
       </c>
@@ -3673,7 +3666,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>651</v>
       </c>
@@ -3684,7 +3677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>655</v>
       </c>
@@ -3695,7 +3688,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>655</v>
       </c>
@@ -3706,7 +3699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>655</v>
       </c>
@@ -3717,7 +3710,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>661</v>
       </c>
@@ -3728,7 +3721,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>661</v>
       </c>
@@ -3739,7 +3732,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>664</v>
       </c>
@@ -3750,7 +3743,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>664</v>
       </c>
@@ -3761,7 +3754,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>669</v>
       </c>
@@ -3772,7 +3765,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>669</v>
       </c>
@@ -3783,7 +3776,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>672</v>
       </c>
@@ -3794,7 +3787,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>672</v>
       </c>
@@ -3805,7 +3798,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>676</v>
       </c>
@@ -3816,7 +3809,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>676</v>
       </c>
@@ -3827,7 +3820,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>678</v>
       </c>
@@ -3838,7 +3831,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>678</v>
       </c>
@@ -3849,7 +3842,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>681</v>
       </c>
@@ -3860,7 +3853,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>681</v>
       </c>
@@ -3871,7 +3864,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>684</v>
       </c>
@@ -3882,7 +3875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>684</v>
       </c>
@@ -3893,7 +3886,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>689</v>
       </c>
@@ -3904,7 +3897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>689</v>
       </c>
@@ -3915,7 +3908,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>693</v>
       </c>
@@ -3926,7 +3919,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>693</v>
       </c>
@@ -3937,7 +3930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>696</v>
       </c>
@@ -3948,7 +3941,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>699</v>
       </c>
@@ -3959,7 +3952,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>702</v>
       </c>
@@ -3970,7 +3963,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>702</v>
       </c>
@@ -3981,7 +3974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>705</v>
       </c>
@@ -3992,7 +3985,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>709</v>
       </c>
@@ -4003,7 +3996,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>712</v>
       </c>
@@ -4014,7 +4007,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>712</v>
       </c>
@@ -4025,7 +4018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>712</v>
       </c>
@@ -4036,7 +4029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>716</v>
       </c>
@@ -4047,7 +4040,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>716</v>
       </c>
@@ -4058,7 +4051,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>718</v>
       </c>
@@ -4069,7 +4062,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>721</v>
       </c>
@@ -4080,7 +4073,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>721</v>
       </c>
@@ -4091,7 +4084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>723</v>
       </c>
@@ -4102,7 +4095,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>723</v>
       </c>
@@ -4113,7 +4106,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>723</v>
       </c>
@@ -4124,7 +4117,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>725</v>
       </c>
@@ -4135,7 +4128,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>725</v>
       </c>
@@ -4146,7 +4139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>725</v>
       </c>
@@ -4157,7 +4150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>728</v>
       </c>
@@ -4168,7 +4161,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>728</v>
       </c>
@@ -4179,7 +4172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>731</v>
       </c>
@@ -4190,7 +4183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>731</v>
       </c>
@@ -4201,7 +4194,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>734</v>
       </c>
@@ -4212,7 +4205,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>734</v>
       </c>
@@ -4223,7 +4216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>734</v>
       </c>
@@ -4234,7 +4227,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>738</v>
       </c>
@@ -4259,11 +4252,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBA55525-5725-432D-8CC7-0A0B7E5373EF}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="D2:Q119"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="D2:T237"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="4:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D2" t="s">
         <v>0</v>
       </c>
@@ -4273,8 +4265,14 @@
       <c r="F2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="R2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D3">
         <v>222</v>
       </c>
@@ -4299,8 +4297,17 @@
       <c r="Q3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R3" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D4">
         <v>362</v>
       </c>
@@ -4328,8 +4335,19 @@
         <f>P4/(N4+O4)*2</f>
         <v>0.16393442622950818</v>
       </c>
-    </row>
-    <row r="5" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>38</v>
+      </c>
+      <c r="S4">
+        <f>ABS(O4-R4)</f>
+        <v>5</v>
+      </c>
+      <c r="T4">
+        <f>2*S4/(O4+R4)</f>
+        <v>0.14084507042253522</v>
+      </c>
+    </row>
+    <row r="5" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D5">
         <v>371</v>
       </c>
@@ -4357,8 +4375,19 @@
         <f t="shared" ref="Q5:Q68" si="2">P5/(N5+O5)*2</f>
         <v>0.37209302325581395</v>
       </c>
-    </row>
-    <row r="6" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <v>54</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:S68" si="3">ABS(O5-R5)</f>
+        <v>3</v>
+      </c>
+      <c r="T5">
+        <f t="shared" ref="T5:T68" si="4">2*S5/(O5+R5)</f>
+        <v>5.7142857142857141E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D6">
         <v>378</v>
       </c>
@@ -4367,6 +4396,9 @@
       </c>
       <c r="F6">
         <v>51</v>
+      </c>
+      <c r="H6" t="s">
+        <v>22</v>
       </c>
       <c r="M6">
         <v>380</v>
@@ -4386,8 +4418,19 @@
         <f t="shared" si="2"/>
         <v>0.72463768115942029</v>
       </c>
-    </row>
-    <row r="7" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <v>93</v>
+      </c>
+      <c r="S6">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>1.06951871657754E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D7">
         <v>380</v>
       </c>
@@ -4422,8 +4465,19 @@
         <f t="shared" si="2"/>
         <v>0.26153846153846155</v>
       </c>
-    </row>
-    <row r="8" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R7">
+        <v>143</v>
+      </c>
+      <c r="S7">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>2.7586206896551724E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D8">
         <v>384</v>
       </c>
@@ -4458,8 +4512,19 @@
         <f t="shared" si="2"/>
         <v>0.46594982078853048</v>
       </c>
-    </row>
-    <row r="9" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R8">
+        <v>158</v>
+      </c>
+      <c r="S8">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>8.4848484848484854E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D9">
         <v>389</v>
       </c>
@@ -4487,8 +4552,19 @@
         <f t="shared" si="2"/>
         <v>0.42539682539682538</v>
       </c>
-    </row>
-    <row r="10" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R9">
+        <v>179</v>
+      </c>
+      <c r="S9">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>6.4864864864864868E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D10">
         <v>393</v>
       </c>
@@ -4516,8 +4592,19 @@
         <f t="shared" si="2"/>
         <v>0.23361823361823361</v>
       </c>
-    </row>
-    <row r="11" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R10">
+        <v>184</v>
+      </c>
+      <c r="S10">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>6.3157894736842107E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D11">
         <v>397</v>
       </c>
@@ -4545,8 +4632,19 @@
         <f t="shared" si="2"/>
         <v>0.20771513353115728</v>
       </c>
-    </row>
-    <row r="12" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R11">
+        <v>180</v>
+      </c>
+      <c r="S11">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D12">
         <v>402</v>
       </c>
@@ -4555,6 +4653,9 @@
       </c>
       <c r="F12">
         <v>186</v>
+      </c>
+      <c r="H12" t="s">
+        <v>24</v>
       </c>
       <c r="M12">
         <v>405</v>
@@ -4574,8 +4675,19 @@
         <f t="shared" si="2"/>
         <v>0.14942528735632185</v>
       </c>
-    </row>
-    <row r="13" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R12">
+        <v>173</v>
+      </c>
+      <c r="S12">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="4"/>
+        <v>7.7777777777777779E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D13">
         <v>405</v>
       </c>
@@ -4584,6 +4696,13 @@
       </c>
       <c r="F13">
         <v>187</v>
+      </c>
+      <c r="H13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13">
+        <f>AVERAGE(S4:S118)</f>
+        <v>4.2695652173913041</v>
       </c>
       <c r="M13">
         <v>408</v>
@@ -4603,8 +4722,19 @@
         <f t="shared" si="2"/>
         <v>9.0261282660332537E-2</v>
       </c>
-    </row>
-    <row r="14" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R13">
+        <v>214</v>
+      </c>
+      <c r="S13">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="4"/>
+        <v>2.7649769585253458E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D14">
         <v>408</v>
       </c>
@@ -4613,6 +4743,13 @@
       </c>
       <c r="F14">
         <v>220</v>
+      </c>
+      <c r="H14" t="s">
+        <v>25</v>
+      </c>
+      <c r="I14" s="2">
+        <f>AVERAGE(T4:T118)</f>
+        <v>9.4306782255471205E-2</v>
       </c>
       <c r="M14">
         <v>411</v>
@@ -4632,8 +4769,19 @@
         <f t="shared" si="2"/>
         <v>0.14958448753462603</v>
       </c>
-    </row>
-    <row r="15" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R14">
+        <v>187</v>
+      </c>
+      <c r="S14">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="T14">
+        <f t="shared" si="4"/>
+        <v>3.6745406824146981E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D15">
         <v>411</v>
       </c>
@@ -4661,8 +4809,19 @@
         <f t="shared" si="2"/>
         <v>0.31688311688311688</v>
       </c>
-    </row>
-    <row r="16" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R15">
+        <v>201</v>
+      </c>
+      <c r="S15">
+        <f t="shared" si="3"/>
+        <v>22</v>
+      </c>
+      <c r="T15">
+        <f t="shared" si="4"/>
+        <v>0.10377358490566038</v>
+      </c>
+    </row>
+    <row r="16" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D16">
         <v>416</v>
       </c>
@@ -4690,8 +4849,19 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R16">
+        <v>171</v>
+      </c>
+      <c r="S16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D17">
         <v>419</v>
       </c>
@@ -4719,8 +4889,19 @@
         <f t="shared" si="2"/>
         <v>7.2727272727272724E-2</v>
       </c>
-    </row>
-    <row r="18" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R17">
+        <v>170</v>
+      </c>
+      <c r="S17">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <f t="shared" si="4"/>
+        <v>5.8651026392961877E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D18">
         <v>422</v>
       </c>
@@ -4748,8 +4929,19 @@
         <f t="shared" si="2"/>
         <v>5.9347181008902079E-3</v>
       </c>
-    </row>
-    <row r="19" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>163</v>
+      </c>
+      <c r="S18">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="T18">
+        <f t="shared" si="4"/>
+        <v>3.0211480362537766E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D19">
         <v>425</v>
       </c>
@@ -4777,8 +4969,19 @@
         <f t="shared" si="2"/>
         <v>0.12857142857142856</v>
       </c>
-    </row>
-    <row r="20" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R19">
+        <v>155</v>
+      </c>
+      <c r="S19">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="T19">
+        <f t="shared" si="4"/>
+        <v>3.9473684210526314E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D20">
         <v>428</v>
       </c>
@@ -4806,8 +5009,19 @@
         <f t="shared" si="2"/>
         <v>7.5313807531380755E-2</v>
       </c>
-    </row>
-    <row r="21" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R20">
+        <v>120</v>
+      </c>
+      <c r="S20">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="T20">
+        <f t="shared" si="4"/>
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D21">
         <v>431</v>
       </c>
@@ -4835,8 +5049,19 @@
         <f t="shared" si="2"/>
         <v>0.21943573667711599</v>
       </c>
-    </row>
-    <row r="22" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>166</v>
+      </c>
+      <c r="S21">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="T21">
+        <f t="shared" si="4"/>
+        <v>6.4139941690962099E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D22">
         <v>433</v>
       </c>
@@ -4864,8 +5089,19 @@
         <f t="shared" si="2"/>
         <v>0.34096692111959287</v>
       </c>
-    </row>
-    <row r="23" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>228</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="4"/>
+        <v>8.7336244541484712E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D23">
         <v>436</v>
       </c>
@@ -4893,8 +5129,19 @@
         <f t="shared" si="2"/>
         <v>0.41833810888252149</v>
       </c>
-    </row>
-    <row r="24" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R23">
+        <v>197</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="4"/>
+        <v>6.8627450980392163E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D24">
         <v>440</v>
       </c>
@@ -4922,8 +5169,19 @@
         <f t="shared" si="2"/>
         <v>0.22372881355932203</v>
       </c>
-    </row>
-    <row r="25" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>155</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="4"/>
+        <v>5.6426332288401257E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D25">
         <v>443</v>
       </c>
@@ -4951,8 +5209,19 @@
         <f t="shared" si="2"/>
         <v>0.49014084507042255</v>
       </c>
-    </row>
-    <row r="26" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R25">
+        <v>200</v>
+      </c>
+      <c r="S25">
+        <f t="shared" si="3"/>
+        <v>21</v>
+      </c>
+      <c r="T25">
+        <f t="shared" si="4"/>
+        <v>9.9762470308788598E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D26">
         <v>446</v>
       </c>
@@ -4980,8 +5249,19 @@
         <f t="shared" si="2"/>
         <v>0.41290322580645161</v>
       </c>
-    </row>
-    <row r="27" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R26">
+        <v>174</v>
+      </c>
+      <c r="S26">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="T26">
+        <f t="shared" si="4"/>
+        <v>7.2022160664819951E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D27">
         <v>450</v>
       </c>
@@ -5009,8 +5289,19 @@
         <f t="shared" si="2"/>
         <v>0.39490445859872614</v>
       </c>
-    </row>
-    <row r="28" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>81</v>
+      </c>
+      <c r="S27">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="T27">
+        <f t="shared" si="4"/>
+        <v>0.14857142857142858</v>
+      </c>
+    </row>
+    <row r="28" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D28">
         <v>453</v>
       </c>
@@ -5038,8 +5329,19 @@
         <f t="shared" si="2"/>
         <v>0.54347826086956519</v>
       </c>
-    </row>
-    <row r="29" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R28">
+        <v>223</v>
+      </c>
+      <c r="S28">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="T28">
+        <f t="shared" si="4"/>
+        <v>4.8140043763676151E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D29">
         <v>455</v>
       </c>
@@ -5067,8 +5369,19 @@
         <f t="shared" si="2"/>
         <v>0.45669291338582679</v>
       </c>
-    </row>
-    <row r="30" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R29">
+        <v>234</v>
+      </c>
+      <c r="S29">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T29">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D30">
         <v>458</v>
       </c>
@@ -5096,8 +5409,19 @@
         <f t="shared" si="2"/>
         <v>1.488833746898263E-2</v>
       </c>
-    </row>
-    <row r="31" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R30">
+        <v>205</v>
+      </c>
+      <c r="S30">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T30">
+        <f t="shared" si="4"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D31">
         <v>461</v>
       </c>
@@ -5125,8 +5449,19 @@
         <f t="shared" si="2"/>
         <v>0.35565819861431869</v>
       </c>
-    </row>
-    <row r="32" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R31">
+        <v>247</v>
+      </c>
+      <c r="S31">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="T31">
+        <f t="shared" si="4"/>
+        <v>3.1872509960159362E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D32">
         <v>466</v>
       </c>
@@ -5154,8 +5489,19 @@
         <f t="shared" si="2"/>
         <v>0.40182648401826482</v>
       </c>
-    </row>
-    <row r="33" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>252</v>
+      </c>
+      <c r="S32">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="T32">
+        <f t="shared" si="4"/>
+        <v>4.2718446601941747E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D33">
         <v>470</v>
       </c>
@@ -5183,8 +5529,19 @@
         <f t="shared" si="2"/>
         <v>5.9701492537313433E-3</v>
       </c>
-    </row>
-    <row r="34" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R33">
+        <v>170</v>
+      </c>
+      <c r="S33">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T33">
+        <f t="shared" si="4"/>
+        <v>1.7804154302670624E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D34">
         <v>473</v>
       </c>
@@ -5212,8 +5569,19 @@
         <f t="shared" si="2"/>
         <v>7.6782449725776969E-2</v>
       </c>
-    </row>
-    <row r="35" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <v>263</v>
+      </c>
+      <c r="S34">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D35">
         <v>475</v>
       </c>
@@ -5241,8 +5609,19 @@
         <f t="shared" si="2"/>
         <v>1.6E-2</v>
       </c>
-    </row>
-    <row r="36" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R35">
+        <v>186</v>
+      </c>
+      <c r="S35">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T35">
+        <f t="shared" si="4"/>
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D36">
         <v>478</v>
       </c>
@@ -5270,8 +5649,19 @@
         <f t="shared" si="2"/>
         <v>6.097560975609756E-2</v>
       </c>
-    </row>
-    <row r="37" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R36">
+        <v>162</v>
+      </c>
+      <c r="S36">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="T36">
+        <f t="shared" si="4"/>
+        <v>4.2296072507552872E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D37">
         <v>481</v>
       </c>
@@ -5299,8 +5689,19 @@
         <f t="shared" si="2"/>
         <v>5.0991501416430593E-2</v>
       </c>
-    </row>
-    <row r="38" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R37">
+        <v>185</v>
+      </c>
+      <c r="S37">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="T37">
+        <f t="shared" si="4"/>
+        <v>2.185792349726776E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D38">
         <v>484</v>
       </c>
@@ -5328,8 +5729,19 @@
         <f t="shared" si="2"/>
         <v>0.33918128654970758</v>
       </c>
-    </row>
-    <row r="39" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R38">
+        <v>202</v>
+      </c>
+      <c r="S38">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T38">
+        <f t="shared" si="4"/>
+        <v>9.9502487562189053E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D39">
         <v>487</v>
       </c>
@@ -5357,8 +5769,19 @@
         <f t="shared" si="2"/>
         <v>4.9689440993788817E-2</v>
       </c>
-    </row>
-    <row r="40" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R39">
+        <v>151</v>
+      </c>
+      <c r="S39">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="T39">
+        <f t="shared" si="4"/>
+        <v>8.8607594936708861E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D40">
         <v>490</v>
       </c>
@@ -5386,8 +5809,19 @@
         <f t="shared" si="2"/>
         <v>0.11570247933884298</v>
       </c>
-    </row>
-    <row r="41" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R40">
+        <v>172</v>
+      </c>
+      <c r="S40">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <f t="shared" si="4"/>
+        <v>5.8309037900874635E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D41">
         <v>495</v>
       </c>
@@ -5415,8 +5849,19 @@
         <f t="shared" si="2"/>
         <v>0.25142857142857145</v>
       </c>
-    </row>
-    <row r="42" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R41">
+        <v>188</v>
+      </c>
+      <c r="S41">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="T41">
+        <f t="shared" si="4"/>
+        <v>4.6753246753246755E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D42">
         <v>499</v>
       </c>
@@ -5444,8 +5889,19 @@
         <f t="shared" si="2"/>
         <v>7.2289156626506021E-2</v>
       </c>
-    </row>
-    <row r="43" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R42">
+        <v>171</v>
+      </c>
+      <c r="S42">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <f t="shared" si="4"/>
+        <v>5.8309037900874635E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D43">
         <v>503</v>
       </c>
@@ -5473,8 +5929,19 @@
         <f t="shared" si="2"/>
         <v>5.1575931232091692E-2</v>
       </c>
-    </row>
-    <row r="44" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R43">
+        <v>180</v>
+      </c>
+      <c r="S43">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <f t="shared" si="4"/>
+        <v>5.5710306406685237E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D44">
         <v>506</v>
       </c>
@@ -5502,8 +5969,19 @@
         <f t="shared" si="2"/>
         <v>3.4188034188034191E-2</v>
       </c>
-    </row>
-    <row r="45" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R44">
+        <v>114</v>
+      </c>
+      <c r="S44">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <f t="shared" si="4"/>
+        <v>8.7336244541484712E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D45">
         <v>509</v>
       </c>
@@ -5531,8 +6009,19 @@
         <f t="shared" si="2"/>
         <v>0.10126582278481013</v>
       </c>
-    </row>
-    <row r="46" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R45">
+        <v>173</v>
+      </c>
+      <c r="S45">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="T45">
+        <f t="shared" si="4"/>
+        <v>4.1297935103244837E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D46">
         <v>512</v>
       </c>
@@ -5560,8 +6049,19 @@
         <f t="shared" si="2"/>
         <v>0.15699658703071673</v>
       </c>
-    </row>
-    <row r="47" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R46">
+        <v>174</v>
+      </c>
+      <c r="S46">
+        <f t="shared" si="3"/>
+        <v>16</v>
+      </c>
+      <c r="T46">
+        <f t="shared" si="4"/>
+        <v>9.6385542168674704E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D47">
         <v>515</v>
       </c>
@@ -5589,8 +6089,19 @@
         <f t="shared" si="2"/>
         <v>6.006006006006006E-3</v>
       </c>
-    </row>
-    <row r="48" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>162</v>
+      </c>
+      <c r="S47">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="T47">
+        <f t="shared" si="4"/>
+        <v>3.0395136778115502E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D48">
         <v>518</v>
       </c>
@@ -5618,8 +6129,19 @@
         <f t="shared" si="2"/>
         <v>0.14180929095354522</v>
       </c>
-    </row>
-    <row r="49" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R48">
+        <v>204</v>
+      </c>
+      <c r="S48">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="T48">
+        <f t="shared" si="4"/>
+        <v>7.0921985815602842E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D49">
         <v>521</v>
       </c>
@@ -5647,8 +6169,19 @@
         <f t="shared" si="2"/>
         <v>0.1388888888888889</v>
       </c>
-    </row>
-    <row r="50" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R49">
+        <v>140</v>
+      </c>
+      <c r="S49">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="T49">
+        <f t="shared" si="4"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D50">
         <v>525</v>
       </c>
@@ -5676,8 +6209,19 @@
         <f t="shared" si="2"/>
         <v>0.30645161290322581</v>
       </c>
-    </row>
-    <row r="51" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R50">
+        <v>131</v>
+      </c>
+      <c r="S50">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="T50">
+        <f t="shared" si="4"/>
+        <v>8.7591240875912413E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D51">
         <v>529</v>
       </c>
@@ -5705,8 +6249,19 @@
         <f t="shared" si="2"/>
         <v>8.5106382978723406E-3</v>
       </c>
-    </row>
-    <row r="52" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R51">
+        <v>136</v>
+      </c>
+      <c r="S51">
+        <f t="shared" si="3"/>
+        <v>18</v>
+      </c>
+      <c r="T51">
+        <f t="shared" si="4"/>
+        <v>0.14173228346456693</v>
+      </c>
+    </row>
+    <row r="52" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D52">
         <v>533</v>
       </c>
@@ -5734,8 +6289,19 @@
         <f t="shared" si="2"/>
         <v>8.3333333333333329E-2</v>
       </c>
-    </row>
-    <row r="53" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R52">
+        <v>124</v>
+      </c>
+      <c r="S52">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T52">
+        <f t="shared" si="4"/>
+        <v>8.0321285140562242E-3</v>
+      </c>
+    </row>
+    <row r="53" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D53">
         <v>536</v>
       </c>
@@ -5763,8 +6329,19 @@
         <f t="shared" si="2"/>
         <v>0.22222222222222221</v>
       </c>
-    </row>
-    <row r="54" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R53">
+        <v>7</v>
+      </c>
+      <c r="S53">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T53">
+        <f t="shared" si="4"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="54" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D54">
         <v>545</v>
       </c>
@@ -5792,8 +6369,19 @@
         <f t="shared" si="2"/>
         <v>0.74285714285714288</v>
       </c>
-    </row>
-    <row r="55" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R54">
+        <v>19</v>
+      </c>
+      <c r="S54">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="T54">
+        <f t="shared" si="4"/>
+        <v>0.23255813953488372</v>
+      </c>
+    </row>
+    <row r="55" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D55">
         <v>547</v>
       </c>
@@ -5821,8 +6409,19 @@
         <f t="shared" si="2"/>
         <v>0.5714285714285714</v>
       </c>
-    </row>
-    <row r="56" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R55">
+        <v>13</v>
+      </c>
+      <c r="S55">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="T55">
+        <f t="shared" si="4"/>
+        <v>0.32258064516129031</v>
+      </c>
+    </row>
+    <row r="56" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D56">
         <v>550</v>
       </c>
@@ -5850,8 +6449,19 @@
         <f t="shared" si="2"/>
         <v>0.23255813953488372</v>
       </c>
-    </row>
-    <row r="57" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R56">
+        <v>25</v>
+      </c>
+      <c r="S56">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T56">
+        <f t="shared" si="4"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D57">
         <v>553</v>
       </c>
@@ -5879,8 +6489,19 @@
         <f t="shared" si="2"/>
         <v>0.19718309859154928</v>
       </c>
-    </row>
-    <row r="58" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R57">
+        <v>36</v>
+      </c>
+      <c r="S57">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T57">
+        <f t="shared" si="4"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="58" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D58">
         <v>556</v>
       </c>
@@ -5908,8 +6529,19 @@
         <f t="shared" si="2"/>
         <v>0.36363636363636365</v>
       </c>
-    </row>
-    <row r="59" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R58">
+        <v>41</v>
+      </c>
+      <c r="S58">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T58">
+        <f t="shared" si="4"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="59" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D59">
         <v>558</v>
       </c>
@@ -5937,8 +6569,19 @@
         <f t="shared" si="2"/>
         <v>0.375</v>
       </c>
-    </row>
-    <row r="60" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R59">
+        <v>38</v>
+      </c>
+      <c r="S59">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D60">
         <v>561</v>
       </c>
@@ -5966,8 +6609,19 @@
         <f t="shared" si="2"/>
         <v>0.18181818181818182</v>
       </c>
-    </row>
-    <row r="61" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R60">
+        <v>26</v>
+      </c>
+      <c r="S60">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T60">
+        <f t="shared" si="4"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="61" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D61">
         <v>564</v>
       </c>
@@ -5995,8 +6649,19 @@
         <f t="shared" si="2"/>
         <v>0.72727272727272729</v>
       </c>
-    </row>
-    <row r="62" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R61">
+        <v>12</v>
+      </c>
+      <c r="S61">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T61">
+        <f t="shared" si="4"/>
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="62" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D62">
         <v>567</v>
       </c>
@@ -6024,8 +6689,19 @@
         <f t="shared" si="2"/>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="63" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R62">
+        <v>13</v>
+      </c>
+      <c r="S62">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T62">
+        <f t="shared" si="4"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="63" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D63">
         <v>569</v>
       </c>
@@ -6053,8 +6729,19 @@
         <f t="shared" si="2"/>
         <v>6.25E-2</v>
       </c>
-    </row>
-    <row r="64" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R63">
+        <v>31</v>
+      </c>
+      <c r="S63">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="T63">
+        <f t="shared" si="4"/>
+        <v>6.25E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D64">
         <v>572</v>
       </c>
@@ -6082,8 +6769,19 @@
         <f t="shared" si="2"/>
         <v>4.6511627906976744E-2</v>
       </c>
-    </row>
-    <row r="65" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R64">
+        <v>19</v>
+      </c>
+      <c r="S64">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T64">
+        <f t="shared" si="4"/>
+        <v>0.14634146341463414</v>
+      </c>
+    </row>
+    <row r="65" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D65">
         <v>574</v>
       </c>
@@ -6111,8 +6809,19 @@
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-    </row>
-    <row r="66" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R65">
+        <v>9</v>
+      </c>
+      <c r="S65">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D66">
         <v>576</v>
       </c>
@@ -6140,8 +6849,19 @@
         <f t="shared" si="2"/>
         <v>6.8965517241379309E-2</v>
       </c>
-    </row>
-    <row r="67" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R66">
+        <v>15</v>
+      </c>
+      <c r="S66">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D67">
         <v>577</v>
       </c>
@@ -6169,8 +6889,19 @@
         <f t="shared" si="2"/>
         <v>4.878048780487805E-2</v>
       </c>
-    </row>
-    <row r="68" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R67">
+        <v>25</v>
+      </c>
+      <c r="S67">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="T67">
+        <f t="shared" si="4"/>
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="68" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D68">
         <v>580</v>
       </c>
@@ -6198,8 +6929,19 @@
         <f t="shared" si="2"/>
         <v>0.19607843137254902</v>
       </c>
-    </row>
-    <row r="69" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R68">
+        <v>25</v>
+      </c>
+      <c r="S68">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="T68">
+        <f t="shared" si="4"/>
+        <v>0.11320754716981132</v>
+      </c>
+    </row>
+    <row r="69" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D69">
         <v>584</v>
       </c>
@@ -6216,19 +6958,30 @@
         <v>17</v>
       </c>
       <c r="O69">
-        <f t="shared" ref="O69:O118" si="3">VLOOKUP(M69,$D$2:$F$119,3,FALSE)</f>
+        <f t="shared" ref="O69:O118" si="5">VLOOKUP(M69,$D$2:$F$119,3,FALSE)</f>
         <v>19</v>
       </c>
       <c r="P69">
-        <f t="shared" ref="P69:P118" si="4">ABS(N69-O69)</f>
+        <f t="shared" ref="P69:P118" si="6">ABS(N69-O69)</f>
         <v>2</v>
       </c>
       <c r="Q69">
-        <f t="shared" ref="Q69:Q118" si="5">P69/(N69+O69)*2</f>
+        <f t="shared" ref="Q69:Q118" si="7">P69/(N69+O69)*2</f>
         <v>0.1111111111111111</v>
       </c>
-    </row>
-    <row r="70" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R69">
+        <v>16</v>
+      </c>
+      <c r="S69">
+        <f t="shared" ref="S69:S118" si="8">ABS(O69-R69)</f>
+        <v>3</v>
+      </c>
+      <c r="T69">
+        <f t="shared" ref="T69:T118" si="9">2*S69/(O69+R69)</f>
+        <v>0.17142857142857143</v>
+      </c>
+    </row>
+    <row r="70" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D70">
         <v>586</v>
       </c>
@@ -6245,19 +6998,30 @@
         <v>3</v>
       </c>
       <c r="O70">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P70">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q70">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.4</v>
       </c>
-    </row>
-    <row r="71" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R70">
+        <v>3</v>
+      </c>
+      <c r="S70">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T70">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D71">
         <v>587</v>
       </c>
@@ -6274,19 +7038,30 @@
         <v>22</v>
       </c>
       <c r="O71">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="P71">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q71">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.5238095238095233E-2</v>
       </c>
-    </row>
-    <row r="72" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R71">
+        <v>22</v>
+      </c>
+      <c r="S71">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T71">
+        <f t="shared" si="9"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D72">
         <v>589</v>
       </c>
@@ -6303,19 +7078,30 @@
         <v>11</v>
       </c>
       <c r="O72">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="P72">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="Q72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.42857142857142855</v>
       </c>
-    </row>
-    <row r="73" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R72">
+        <v>15</v>
+      </c>
+      <c r="S72">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T72">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="73" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D73">
         <v>592</v>
       </c>
@@ -6332,19 +7118,30 @@
         <v>12</v>
       </c>
       <c r="O73">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="P73">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>11</v>
       </c>
       <c r="Q73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.62857142857142856</v>
       </c>
-    </row>
-    <row r="74" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R73">
+        <v>23</v>
+      </c>
+      <c r="S73">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D74">
         <v>594</v>
       </c>
@@ -6361,19 +7158,30 @@
         <v>17</v>
       </c>
       <c r="O74">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>17</v>
       </c>
       <c r="P74">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R74">
+        <v>15</v>
+      </c>
+      <c r="S74">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T74">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="75" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D75">
         <v>596</v>
       </c>
@@ -6390,19 +7198,30 @@
         <v>12</v>
       </c>
       <c r="O75">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="P75">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="Q75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.2857142857142857</v>
       </c>
-    </row>
-    <row r="76" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R75">
+        <v>16</v>
+      </c>
+      <c r="S75">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D76">
         <v>598</v>
       </c>
@@ -6419,19 +7238,30 @@
         <v>31</v>
       </c>
       <c r="O76">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="P76">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.2786885245901641E-2</v>
       </c>
-    </row>
-    <row r="77" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R76">
+        <v>33</v>
+      </c>
+      <c r="S76">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T76">
+        <f t="shared" si="9"/>
+        <v>9.5238095238095233E-2</v>
+      </c>
+    </row>
+    <row r="77" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D77">
         <v>601</v>
       </c>
@@ -6448,19 +7278,30 @@
         <v>19</v>
       </c>
       <c r="O77">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="P77">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5.128205128205128E-2</v>
       </c>
-    </row>
-    <row r="78" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R77">
+        <v>19</v>
+      </c>
+      <c r="S77">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T77">
+        <f t="shared" si="9"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+    </row>
+    <row r="78" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D78">
         <v>603</v>
       </c>
@@ -6477,19 +7318,30 @@
         <v>49</v>
       </c>
       <c r="O78">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>49</v>
       </c>
       <c r="P78">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R78">
+        <v>50</v>
+      </c>
+      <c r="S78">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T78">
+        <f t="shared" si="9"/>
+        <v>2.0202020202020204E-2</v>
+      </c>
+    </row>
+    <row r="79" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D79">
         <v>606</v>
       </c>
@@ -6506,19 +7358,30 @@
         <v>40</v>
       </c>
       <c r="O79">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>44</v>
       </c>
       <c r="P79">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="Q79">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.5238095238095233E-2</v>
       </c>
-    </row>
-    <row r="80" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R79">
+        <v>46</v>
+      </c>
+      <c r="S79">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T79">
+        <f t="shared" si="9"/>
+        <v>4.4444444444444446E-2</v>
+      </c>
+    </row>
+    <row r="80" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D80">
         <v>609</v>
       </c>
@@ -6535,19 +7398,30 @@
         <v>28</v>
       </c>
       <c r="O80">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="P80">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q80">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.11320754716981132</v>
       </c>
-    </row>
-    <row r="81" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R80">
+        <v>25</v>
+      </c>
+      <c r="S80">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T80">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D81">
         <v>612</v>
       </c>
@@ -6564,19 +7438,30 @@
         <v>37</v>
       </c>
       <c r="O81">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
       <c r="P81">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Q81">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.12658227848101267</v>
       </c>
-    </row>
-    <row r="82" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R81">
+        <v>40</v>
+      </c>
+      <c r="S81">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T81">
+        <f t="shared" si="9"/>
+        <v>4.878048780487805E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D82">
         <v>615</v>
       </c>
@@ -6593,19 +7478,30 @@
         <v>21</v>
       </c>
       <c r="O82">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="P82">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q82">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.13333333333333333</v>
       </c>
-    </row>
-    <row r="83" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R82">
+        <v>24</v>
+      </c>
+      <c r="S82">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T82">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D83">
         <v>618</v>
       </c>
@@ -6622,19 +7518,30 @@
         <v>25</v>
       </c>
       <c r="O83">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="P83">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q83">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R83">
+        <v>27</v>
+      </c>
+      <c r="S83">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T83">
+        <f t="shared" si="9"/>
+        <v>7.6923076923076927E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D84">
         <v>621</v>
       </c>
@@ -6651,19 +7558,30 @@
         <v>23</v>
       </c>
       <c r="O84">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="P84">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q84">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.13953488372093023</v>
       </c>
-    </row>
-    <row r="85" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R84">
+        <v>20</v>
+      </c>
+      <c r="S84">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T84">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D85">
         <v>624</v>
       </c>
@@ -6680,19 +7598,30 @@
         <v>17</v>
       </c>
       <c r="O85">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="P85">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q85">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6.0606060606060608E-2</v>
       </c>
-    </row>
-    <row r="86" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R85">
+        <v>17</v>
+      </c>
+      <c r="S85">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T85">
+        <f t="shared" si="9"/>
+        <v>6.0606060606060608E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D86">
         <v>627</v>
       </c>
@@ -6709,19 +7638,30 @@
         <v>4</v>
       </c>
       <c r="O86">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="P86">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q86">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="87" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R86">
+        <v>4</v>
+      </c>
+      <c r="S86">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T86">
+        <f t="shared" si="9"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="87" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D87">
         <v>628</v>
       </c>
@@ -6738,19 +7678,30 @@
         <v>10</v>
       </c>
       <c r="O87">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>16</v>
       </c>
       <c r="P87">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="Q87">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.46153846153846156</v>
       </c>
-    </row>
-    <row r="88" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R87">
+        <v>16</v>
+      </c>
+      <c r="S87">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T87">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D88">
         <v>633</v>
       </c>
@@ -6767,19 +7718,30 @@
         <v>4</v>
       </c>
       <c r="O88">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="P88">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="Q88">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="89" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R88">
+        <v>12</v>
+      </c>
+      <c r="S88">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="T88">
+        <f t="shared" si="9"/>
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="89" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D89">
         <v>637</v>
       </c>
@@ -6796,19 +7758,30 @@
         <v>6</v>
       </c>
       <c r="O89">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="P89">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q89">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.15384615384615385</v>
       </c>
-    </row>
-    <row r="90" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R89">
+        <v>8</v>
+      </c>
+      <c r="S89">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T89">
+        <f t="shared" si="9"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="90" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D90">
         <v>640</v>
       </c>
@@ -6825,19 +7798,30 @@
         <v>20</v>
       </c>
       <c r="O90">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="P90">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q90">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R90">
+        <v>20</v>
+      </c>
+      <c r="S90">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T90">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D91">
         <v>645</v>
       </c>
@@ -6854,19 +7838,30 @@
         <v>20</v>
       </c>
       <c r="O91">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>22</v>
       </c>
       <c r="P91">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q91">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.5238095238095233E-2</v>
       </c>
-    </row>
-    <row r="92" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R91">
+        <v>24</v>
+      </c>
+      <c r="S91">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T91">
+        <f t="shared" si="9"/>
+        <v>8.6956521739130432E-2</v>
+      </c>
+    </row>
+    <row r="92" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D92">
         <v>648</v>
       </c>
@@ -6883,19 +7878,30 @@
         <v>6</v>
       </c>
       <c r="O92">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="P92">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q92">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.18181818181818182</v>
       </c>
-    </row>
-    <row r="93" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R92">
+        <v>5</v>
+      </c>
+      <c r="S92">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T92">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D93">
         <v>651</v>
       </c>
@@ -6912,19 +7918,30 @@
         <v>9</v>
       </c>
       <c r="O93">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="P93">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q93">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.2857142857142857</v>
       </c>
-    </row>
-    <row r="94" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R93">
+        <v>12</v>
+      </c>
+      <c r="S93">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T93">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D94">
         <v>655</v>
       </c>
@@ -6941,19 +7958,30 @@
         <v>13</v>
       </c>
       <c r="O94">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="P94">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q94">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.14285714285714285</v>
       </c>
-    </row>
-    <row r="95" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R94">
+        <v>13</v>
+      </c>
+      <c r="S94">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T94">
+        <f t="shared" si="9"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+    <row r="95" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D95">
         <v>661</v>
       </c>
@@ -6970,19 +7998,30 @@
         <v>12</v>
       </c>
       <c r="O95">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="P95">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q95">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-    </row>
-    <row r="96" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R95">
+        <v>13</v>
+      </c>
+      <c r="S95">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T95">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D96">
         <v>664</v>
       </c>
@@ -6999,19 +8038,30 @@
         <v>15</v>
       </c>
       <c r="O96">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="P96">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q96">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R96">
+        <v>14</v>
+      </c>
+      <c r="S96">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T96">
+        <f t="shared" si="9"/>
+        <v>6.8965517241379309E-2</v>
+      </c>
+    </row>
+    <row r="97" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D97">
         <v>669</v>
       </c>
@@ -7028,19 +8078,30 @@
         <v>8</v>
       </c>
       <c r="O97">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>5</v>
       </c>
       <c r="P97">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q97">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.46153846153846156</v>
       </c>
-    </row>
-    <row r="98" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R97">
+        <v>10</v>
+      </c>
+      <c r="S97">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="T97">
+        <f t="shared" si="9"/>
+        <v>0.66666666666666663</v>
+      </c>
+    </row>
+    <row r="98" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D98">
         <v>672</v>
       </c>
@@ -7057,19 +8118,30 @@
         <v>14</v>
       </c>
       <c r="O98">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>14</v>
       </c>
       <c r="P98">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q98">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R98">
+        <v>14</v>
+      </c>
+      <c r="S98">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T98">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D99">
         <v>676</v>
       </c>
@@ -7086,19 +8158,30 @@
         <v>15</v>
       </c>
       <c r="O99">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="P99">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q99">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R99">
+        <v>17</v>
+      </c>
+      <c r="S99">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T99">
+        <f t="shared" si="9"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="100" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D100">
         <v>678</v>
       </c>
@@ -7115,19 +8198,30 @@
         <v>25</v>
       </c>
       <c r="O100">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="P100">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q100">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4.0816326530612242E-2</v>
       </c>
-    </row>
-    <row r="101" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R100">
+        <v>25</v>
+      </c>
+      <c r="S100">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T100">
+        <f t="shared" si="9"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="101" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D101">
         <v>681</v>
       </c>
@@ -7144,19 +8238,30 @@
         <v>31</v>
       </c>
       <c r="O101">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="P101">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q101">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>3.2786885245901641E-2</v>
       </c>
-    </row>
-    <row r="102" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R101">
+        <v>31</v>
+      </c>
+      <c r="S101">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T101">
+        <f t="shared" si="9"/>
+        <v>3.2786885245901641E-2</v>
+      </c>
+    </row>
+    <row r="102" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D102">
         <v>684</v>
       </c>
@@ -7173,19 +8278,30 @@
         <v>19</v>
       </c>
       <c r="O102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>25</v>
       </c>
       <c r="P102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="Q102">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.27272727272727271</v>
       </c>
-    </row>
-    <row r="103" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R102">
+        <v>24</v>
+      </c>
+      <c r="S102">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T102">
+        <f t="shared" si="9"/>
+        <v>4.0816326530612242E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D103">
         <v>689</v>
       </c>
@@ -7202,19 +8318,30 @@
         <v>24</v>
       </c>
       <c r="O103">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>24</v>
       </c>
       <c r="P103">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q103">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="104" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R103">
+        <v>24</v>
+      </c>
+      <c r="S103">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D104">
         <v>693</v>
       </c>
@@ -7231,19 +8358,30 @@
         <v>20</v>
       </c>
       <c r="O104">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>20</v>
       </c>
       <c r="P104">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q104">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="105" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R104">
+        <v>19</v>
+      </c>
+      <c r="S104">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T104">
+        <f t="shared" si="9"/>
+        <v>5.128205128205128E-2</v>
+      </c>
+    </row>
+    <row r="105" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D105">
         <v>696</v>
       </c>
@@ -7260,19 +8398,30 @@
         <v>12</v>
       </c>
       <c r="O105">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="P105">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q105">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.08</v>
       </c>
-    </row>
-    <row r="106" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R105">
+        <v>16</v>
+      </c>
+      <c r="S105">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T105">
+        <f t="shared" si="9"/>
+        <v>0.20689655172413793</v>
+      </c>
+    </row>
+    <row r="106" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D106">
         <v>699</v>
       </c>
@@ -7289,19 +8438,30 @@
         <v>4</v>
       </c>
       <c r="O106">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>8</v>
       </c>
       <c r="P106">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="Q106">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="107" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R106">
+        <v>6</v>
+      </c>
+      <c r="S106">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T106">
+        <f t="shared" si="9"/>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="107" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D107">
         <v>702</v>
       </c>
@@ -7318,19 +8478,30 @@
         <v>16</v>
       </c>
       <c r="O107">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>15</v>
       </c>
       <c r="P107">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q107">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>6.4516129032258063E-2</v>
       </c>
-    </row>
-    <row r="108" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R107">
+        <v>18</v>
+      </c>
+      <c r="S107">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T107">
+        <f t="shared" si="9"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="108" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D108">
         <v>705</v>
       </c>
@@ -7347,19 +8518,30 @@
         <v>18</v>
       </c>
       <c r="O108">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="P108">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q108">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>5.4054054054054057E-2</v>
       </c>
-    </row>
-    <row r="109" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R108">
+        <v>22</v>
+      </c>
+      <c r="S108">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T108">
+        <f t="shared" si="9"/>
+        <v>0.14634146341463414</v>
+      </c>
+    </row>
+    <row r="109" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D109">
         <v>709</v>
       </c>
@@ -7376,19 +8558,30 @@
         <v>2</v>
       </c>
       <c r="O109">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="P109">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q109">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="110" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R109">
+        <v>3</v>
+      </c>
+      <c r="S109">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T109">
+        <f t="shared" si="9"/>
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="110" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D110">
         <v>712</v>
       </c>
@@ -7405,19 +8598,30 @@
         <v>15</v>
       </c>
       <c r="O110">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="P110">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="Q110">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="111" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R110">
+        <v>22</v>
+      </c>
+      <c r="S110">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T110">
+        <f t="shared" si="9"/>
+        <v>4.6511627906976744E-2</v>
+      </c>
+    </row>
+    <row r="111" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D111">
         <v>716</v>
       </c>
@@ -7434,19 +8638,30 @@
         <v>23</v>
       </c>
       <c r="O111">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>21</v>
       </c>
       <c r="P111">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="Q111">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>9.0909090909090912E-2</v>
       </c>
-    </row>
-    <row r="112" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R111">
+        <v>24</v>
+      </c>
+      <c r="S111">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T111">
+        <f t="shared" si="9"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="112" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D112">
         <v>718</v>
       </c>
@@ -7463,19 +8678,30 @@
         <v>16</v>
       </c>
       <c r="O112">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="P112">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="Q112">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.17142857142857143</v>
       </c>
-    </row>
-    <row r="113" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R112">
+        <v>18</v>
+      </c>
+      <c r="S112">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T112">
+        <f t="shared" si="9"/>
+        <v>5.4054054054054057E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D113">
         <v>721</v>
       </c>
@@ -7492,19 +8718,30 @@
         <v>26</v>
       </c>
       <c r="O113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>19</v>
       </c>
       <c r="P113">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="Q113">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.31111111111111112</v>
       </c>
-    </row>
-    <row r="114" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R113">
+        <v>27</v>
+      </c>
+      <c r="S113">
+        <f t="shared" si="8"/>
+        <v>8</v>
+      </c>
+      <c r="T113">
+        <f t="shared" si="9"/>
+        <v>0.34782608695652173</v>
+      </c>
+    </row>
+    <row r="114" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D114">
         <v>723</v>
       </c>
@@ -7521,19 +8758,30 @@
         <v>18</v>
       </c>
       <c r="O114">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>13</v>
       </c>
       <c r="P114">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Q114">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.32258064516129031</v>
       </c>
-    </row>
-    <row r="115" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R114">
+        <v>18</v>
+      </c>
+      <c r="S114">
+        <f t="shared" si="8"/>
+        <v>5</v>
+      </c>
+      <c r="T114">
+        <f t="shared" si="9"/>
+        <v>0.32258064516129031</v>
+      </c>
+    </row>
+    <row r="115" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D115">
         <v>725</v>
       </c>
@@ -7550,19 +8798,30 @@
         <v>18</v>
       </c>
       <c r="O115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>23</v>
       </c>
       <c r="P115">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="Q115">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.24390243902439024</v>
       </c>
-    </row>
-    <row r="116" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R115">
+        <v>23</v>
+      </c>
+      <c r="S115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T115">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D116">
         <v>728</v>
       </c>
@@ -7579,19 +8838,30 @@
         <v>6</v>
       </c>
       <c r="O116">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="P116">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q116">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0.15384615384615385</v>
       </c>
-    </row>
-    <row r="117" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R116">
+        <v>10</v>
+      </c>
+      <c r="S116">
+        <f t="shared" si="8"/>
+        <v>3</v>
+      </c>
+      <c r="T116">
+        <f t="shared" si="9"/>
+        <v>0.35294117647058826</v>
+      </c>
+    </row>
+    <row r="117" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D117">
         <v>731</v>
       </c>
@@ -7608,19 +8878,30 @@
         <v>7</v>
       </c>
       <c r="O117">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>7</v>
       </c>
       <c r="P117">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q117">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="118" spans="4:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="R117">
+        <v>8</v>
+      </c>
+      <c r="S117">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+      <c r="T117">
+        <f t="shared" si="9"/>
+        <v>0.13333333333333333</v>
+      </c>
+    </row>
+    <row r="118" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D118">
         <v>734</v>
       </c>
@@ -7637,19 +8918,30 @@
         <v>11</v>
       </c>
       <c r="O118">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>12</v>
       </c>
       <c r="P118">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="Q118">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>8.6956521739130432E-2</v>
       </c>
-    </row>
-    <row r="119" spans="4:17" x14ac:dyDescent="0.25">
+      <c r="R118">
+        <v>10</v>
+      </c>
+      <c r="S118">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+      <c r="T118">
+        <f t="shared" si="9"/>
+        <v>0.18181818181818182</v>
+      </c>
+    </row>
+    <row r="119" spans="4:20" x14ac:dyDescent="0.3">
       <c r="D119">
         <v>738</v>
       </c>
@@ -7660,16 +8952,1747 @@
         <v>12</v>
       </c>
     </row>
+    <row r="122" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K122" t="s">
+        <v>0</v>
+      </c>
+      <c r="L122" t="s">
+        <v>2</v>
+      </c>
+      <c r="M122" t="s">
+        <v>29</v>
+      </c>
+      <c r="N122" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="123" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K123">
+        <v>371</v>
+      </c>
+      <c r="L123">
+        <f t="shared" ref="L123:L154" si="10">VLOOKUP(K123,$D$2:$F$119,3,FALSE)</f>
+        <v>33</v>
+      </c>
+      <c r="M123">
+        <v>28</v>
+      </c>
+      <c r="N123">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="124" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K124">
+        <v>378</v>
+      </c>
+      <c r="L124">
+        <f t="shared" si="10"/>
+        <v>51</v>
+      </c>
+      <c r="M124">
+        <v>35</v>
+      </c>
+      <c r="N124">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="125" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K125">
+        <v>380</v>
+      </c>
+      <c r="L125">
+        <f t="shared" si="10"/>
+        <v>94</v>
+      </c>
+      <c r="M125">
+        <v>44</v>
+      </c>
+      <c r="N125">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="126" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K126">
+        <v>384</v>
+      </c>
+      <c r="L126">
+        <f t="shared" si="10"/>
+        <v>147</v>
+      </c>
+      <c r="M126">
+        <v>113</v>
+      </c>
+      <c r="N126">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K127">
+        <v>389</v>
+      </c>
+      <c r="L127">
+        <f t="shared" si="10"/>
+        <v>172</v>
+      </c>
+      <c r="M127">
+        <v>107</v>
+      </c>
+      <c r="N127">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="128" spans="4:20" x14ac:dyDescent="0.3">
+      <c r="K128">
+        <v>393</v>
+      </c>
+      <c r="L128">
+        <f t="shared" si="10"/>
+        <v>191</v>
+      </c>
+      <c r="M128">
+        <v>124</v>
+      </c>
+      <c r="N128">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="129" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K129">
+        <v>397</v>
+      </c>
+      <c r="L129">
+        <f t="shared" si="10"/>
+        <v>196</v>
+      </c>
+      <c r="M129">
+        <v>155</v>
+      </c>
+      <c r="N129">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="130" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K130">
+        <v>402</v>
+      </c>
+      <c r="L130">
+        <f t="shared" si="10"/>
+        <v>186</v>
+      </c>
+      <c r="M130">
+        <v>151</v>
+      </c>
+      <c r="N130">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="131" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K131">
+        <v>405</v>
+      </c>
+      <c r="L131">
+        <f t="shared" si="10"/>
+        <v>187</v>
+      </c>
+      <c r="M131">
+        <v>161</v>
+      </c>
+      <c r="N131">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="132" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K132">
+        <v>408</v>
+      </c>
+      <c r="L132">
+        <f t="shared" si="10"/>
+        <v>220</v>
+      </c>
+      <c r="M132">
+        <v>201</v>
+      </c>
+      <c r="N132">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="133" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K133">
+        <v>411</v>
+      </c>
+      <c r="L133">
+        <f t="shared" si="10"/>
+        <v>194</v>
+      </c>
+      <c r="M133">
+        <v>167</v>
+      </c>
+      <c r="N133">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="134" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K134">
+        <v>416</v>
+      </c>
+      <c r="L134">
+        <f t="shared" si="10"/>
+        <v>223</v>
+      </c>
+      <c r="M134">
+        <v>162</v>
+      </c>
+      <c r="N134">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="135" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K135">
+        <v>419</v>
+      </c>
+      <c r="L135">
+        <f t="shared" si="10"/>
+        <v>171</v>
+      </c>
+      <c r="M135">
+        <v>171</v>
+      </c>
+      <c r="N135">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="136" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K136">
+        <v>422</v>
+      </c>
+      <c r="L136">
+        <f t="shared" si="10"/>
+        <v>171</v>
+      </c>
+      <c r="M136">
+        <v>159</v>
+      </c>
+      <c r="N136">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="137" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K137">
+        <v>425</v>
+      </c>
+      <c r="L137">
+        <f t="shared" si="10"/>
+        <v>168</v>
+      </c>
+      <c r="M137">
+        <v>169</v>
+      </c>
+      <c r="N137">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="138" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K138">
+        <v>428</v>
+      </c>
+      <c r="L138">
+        <f t="shared" si="10"/>
+        <v>149</v>
+      </c>
+      <c r="M138">
+        <v>131</v>
+      </c>
+      <c r="N138">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="139" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K139">
+        <v>431</v>
+      </c>
+      <c r="L139">
+        <f t="shared" si="10"/>
+        <v>124</v>
+      </c>
+      <c r="M139">
+        <v>115</v>
+      </c>
+      <c r="N139">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K140">
+        <v>433</v>
+      </c>
+      <c r="L140">
+        <f t="shared" si="10"/>
+        <v>177</v>
+      </c>
+      <c r="M140">
+        <v>142</v>
+      </c>
+      <c r="N140">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="141" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K141">
+        <v>436</v>
+      </c>
+      <c r="L141">
+        <f t="shared" si="10"/>
+        <v>230</v>
+      </c>
+      <c r="M141">
+        <v>163</v>
+      </c>
+      <c r="N141">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="142" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K142">
+        <v>440</v>
+      </c>
+      <c r="L142">
+        <f t="shared" si="10"/>
+        <v>211</v>
+      </c>
+      <c r="M142">
+        <v>138</v>
+      </c>
+      <c r="N142">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="143" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K143">
+        <v>443</v>
+      </c>
+      <c r="L143">
+        <f t="shared" si="10"/>
+        <v>164</v>
+      </c>
+      <c r="M143">
+        <v>131</v>
+      </c>
+      <c r="N143">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="144" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K144">
+        <v>446</v>
+      </c>
+      <c r="L144">
+        <f t="shared" si="10"/>
+        <v>221</v>
+      </c>
+      <c r="M144">
+        <v>134</v>
+      </c>
+      <c r="N144">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="145" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K145">
+        <v>450</v>
+      </c>
+      <c r="L145">
+        <f t="shared" si="10"/>
+        <v>187</v>
+      </c>
+      <c r="M145">
+        <v>123</v>
+      </c>
+      <c r="N145">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="146" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K146">
+        <v>453</v>
+      </c>
+      <c r="L146">
+        <f t="shared" si="10"/>
+        <v>94</v>
+      </c>
+      <c r="M146">
+        <v>63</v>
+      </c>
+      <c r="N146">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="147" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K147">
+        <v>455</v>
+      </c>
+      <c r="L147">
+        <f t="shared" si="10"/>
+        <v>234</v>
+      </c>
+      <c r="M147">
+        <v>134</v>
+      </c>
+      <c r="N147">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="148" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K148">
+        <v>458</v>
+      </c>
+      <c r="L148">
+        <f t="shared" si="10"/>
+        <v>234</v>
+      </c>
+      <c r="M148">
+        <v>147</v>
+      </c>
+      <c r="N148">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="149" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K149">
+        <v>461</v>
+      </c>
+      <c r="L149">
+        <f t="shared" si="10"/>
+        <v>203</v>
+      </c>
+      <c r="M149">
+        <v>200</v>
+      </c>
+      <c r="N149">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="150" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K150">
+        <v>466</v>
+      </c>
+      <c r="L150">
+        <f t="shared" si="10"/>
+        <v>255</v>
+      </c>
+      <c r="M150">
+        <v>178</v>
+      </c>
+      <c r="N150">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="151" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K151">
+        <v>470</v>
+      </c>
+      <c r="L151">
+        <f t="shared" si="10"/>
+        <v>263</v>
+      </c>
+      <c r="M151">
+        <v>175</v>
+      </c>
+      <c r="N151">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="152" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K152">
+        <v>473</v>
+      </c>
+      <c r="L152">
+        <f t="shared" si="10"/>
+        <v>167</v>
+      </c>
+      <c r="M152">
+        <v>168</v>
+      </c>
+      <c r="N152">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="153" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K153">
+        <v>475</v>
+      </c>
+      <c r="L153">
+        <f t="shared" si="10"/>
+        <v>263</v>
+      </c>
+      <c r="M153">
+        <v>284</v>
+      </c>
+      <c r="N153">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="154" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K154">
+        <v>478</v>
+      </c>
+      <c r="L154">
+        <f t="shared" si="10"/>
+        <v>189</v>
+      </c>
+      <c r="M154">
+        <v>186</v>
+      </c>
+      <c r="N154">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="155" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K155">
+        <v>481</v>
+      </c>
+      <c r="L155">
+        <f t="shared" ref="L155:L186" si="11">VLOOKUP(K155,$D$2:$F$119,3,FALSE)</f>
+        <v>169</v>
+      </c>
+      <c r="M155">
+        <v>159</v>
+      </c>
+      <c r="N155">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="156" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K156">
+        <v>484</v>
+      </c>
+      <c r="L156">
+        <f t="shared" si="11"/>
+        <v>181</v>
+      </c>
+      <c r="M156">
+        <v>172</v>
+      </c>
+      <c r="N156">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="157" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K157">
+        <v>487</v>
+      </c>
+      <c r="L157">
+        <f t="shared" si="11"/>
+        <v>200</v>
+      </c>
+      <c r="M157">
+        <v>142</v>
+      </c>
+      <c r="N157">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="158" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K158">
+        <v>490</v>
+      </c>
+      <c r="L158">
+        <f t="shared" si="11"/>
+        <v>165</v>
+      </c>
+      <c r="M158">
+        <v>157</v>
+      </c>
+      <c r="N158">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="159" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K159">
+        <v>495</v>
+      </c>
+      <c r="L159">
+        <f t="shared" si="11"/>
+        <v>171</v>
+      </c>
+      <c r="M159">
+        <v>192</v>
+      </c>
+      <c r="N159">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="160" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K160">
+        <v>499</v>
+      </c>
+      <c r="L160">
+        <f t="shared" si="11"/>
+        <v>197</v>
+      </c>
+      <c r="M160">
+        <v>153</v>
+      </c>
+      <c r="N160">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="161" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K161">
+        <v>503</v>
+      </c>
+      <c r="L161">
+        <f t="shared" si="11"/>
+        <v>172</v>
+      </c>
+      <c r="M161">
+        <v>160</v>
+      </c>
+      <c r="N161">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="162" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K162">
+        <v>506</v>
+      </c>
+      <c r="L162">
+        <f t="shared" si="11"/>
+        <v>179</v>
+      </c>
+      <c r="M162">
+        <v>170</v>
+      </c>
+      <c r="N162">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="163" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K163">
+        <v>509</v>
+      </c>
+      <c r="L163">
+        <f t="shared" si="11"/>
+        <v>115</v>
+      </c>
+      <c r="M163">
+        <v>119</v>
+      </c>
+      <c r="N163">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="164" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K164">
+        <v>512</v>
+      </c>
+      <c r="L164">
+        <f t="shared" si="11"/>
+        <v>166</v>
+      </c>
+      <c r="M164">
+        <v>150</v>
+      </c>
+      <c r="N164">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K165">
+        <v>515</v>
+      </c>
+      <c r="L165">
+        <f t="shared" si="11"/>
+        <v>158</v>
+      </c>
+      <c r="M165">
+        <v>135</v>
+      </c>
+      <c r="N165">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K166">
+        <v>518</v>
+      </c>
+      <c r="L166">
+        <f t="shared" si="11"/>
+        <v>167</v>
+      </c>
+      <c r="M166">
+        <v>166</v>
+      </c>
+      <c r="N166">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K167">
+        <v>521</v>
+      </c>
+      <c r="L167">
+        <f t="shared" si="11"/>
+        <v>219</v>
+      </c>
+      <c r="M167">
+        <v>190</v>
+      </c>
+      <c r="N167">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="168" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K168">
+        <v>525</v>
+      </c>
+      <c r="L168">
+        <f t="shared" si="11"/>
+        <v>154</v>
+      </c>
+      <c r="M168">
+        <v>134</v>
+      </c>
+      <c r="N168">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="169" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K169">
+        <v>529</v>
+      </c>
+      <c r="L169">
+        <f t="shared" si="11"/>
+        <v>143</v>
+      </c>
+      <c r="M169">
+        <v>105</v>
+      </c>
+      <c r="N169">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="170" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K170">
+        <v>533</v>
+      </c>
+      <c r="L170">
+        <f t="shared" si="11"/>
+        <v>118</v>
+      </c>
+      <c r="M170">
+        <v>117</v>
+      </c>
+      <c r="N170">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="171" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K171">
+        <v>536</v>
+      </c>
+      <c r="L171">
+        <f t="shared" si="11"/>
+        <v>125</v>
+      </c>
+      <c r="M171">
+        <v>115</v>
+      </c>
+      <c r="N171">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="172" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K172">
+        <v>545</v>
+      </c>
+      <c r="L172">
+        <f t="shared" si="11"/>
+        <v>10</v>
+      </c>
+      <c r="M172">
+        <v>8</v>
+      </c>
+      <c r="N172">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="173" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K173">
+        <v>547</v>
+      </c>
+      <c r="L173">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="M173">
+        <v>11</v>
+      </c>
+      <c r="N173">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="174" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K174">
+        <v>550</v>
+      </c>
+      <c r="L174">
+        <f t="shared" si="11"/>
+        <v>18</v>
+      </c>
+      <c r="M174">
+        <v>10</v>
+      </c>
+      <c r="N174">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K175">
+        <v>553</v>
+      </c>
+      <c r="L175">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="M175">
+        <v>19</v>
+      </c>
+      <c r="N175">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K176">
+        <v>556</v>
+      </c>
+      <c r="L176">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="M176">
+        <v>32</v>
+      </c>
+      <c r="N176">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="177" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K177">
+        <v>558</v>
+      </c>
+      <c r="L177">
+        <f t="shared" si="11"/>
+        <v>39</v>
+      </c>
+      <c r="M177">
+        <v>27</v>
+      </c>
+      <c r="N177">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K178">
+        <v>561</v>
+      </c>
+      <c r="L178">
+        <f t="shared" si="11"/>
+        <v>38</v>
+      </c>
+      <c r="M178">
+        <v>26</v>
+      </c>
+      <c r="N178">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="179" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K179">
+        <v>564</v>
+      </c>
+      <c r="L179">
+        <f t="shared" si="11"/>
+        <v>24</v>
+      </c>
+      <c r="M179">
+        <v>20</v>
+      </c>
+      <c r="N179">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="180" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K180">
+        <v>567</v>
+      </c>
+      <c r="L180">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="M180">
+        <v>7</v>
+      </c>
+      <c r="N180">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="181" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K181">
+        <v>569</v>
+      </c>
+      <c r="L181">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="M181">
+        <v>10</v>
+      </c>
+      <c r="N181">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K182">
+        <v>572</v>
+      </c>
+      <c r="L182">
+        <f t="shared" si="11"/>
+        <v>33</v>
+      </c>
+      <c r="M182">
+        <v>31</v>
+      </c>
+      <c r="N182">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="183" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K183">
+        <v>574</v>
+      </c>
+      <c r="L183">
+        <f t="shared" si="11"/>
+        <v>22</v>
+      </c>
+      <c r="M183">
+        <v>21</v>
+      </c>
+      <c r="N183">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="184" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K184">
+        <v>576</v>
+      </c>
+      <c r="L184">
+        <f t="shared" si="11"/>
+        <v>9</v>
+      </c>
+      <c r="M184">
+        <v>11</v>
+      </c>
+      <c r="N184">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="185" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K185">
+        <v>577</v>
+      </c>
+      <c r="L185">
+        <f t="shared" si="11"/>
+        <v>15</v>
+      </c>
+      <c r="M185">
+        <v>14</v>
+      </c>
+      <c r="N185">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="186" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K186">
+        <v>580</v>
+      </c>
+      <c r="L186">
+        <f t="shared" si="11"/>
+        <v>20</v>
+      </c>
+      <c r="M186">
+        <v>21</v>
+      </c>
+      <c r="N186">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K187">
+        <v>584</v>
+      </c>
+      <c r="L187">
+        <f t="shared" ref="L187:L218" si="12">VLOOKUP(K187,$D$2:$F$119,3,FALSE)</f>
+        <v>28</v>
+      </c>
+      <c r="M187">
+        <v>23</v>
+      </c>
+      <c r="N187">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K188">
+        <v>586</v>
+      </c>
+      <c r="L188">
+        <f t="shared" si="12"/>
+        <v>19</v>
+      </c>
+      <c r="M188">
+        <v>17</v>
+      </c>
+      <c r="N188">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="189" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K189">
+        <v>587</v>
+      </c>
+      <c r="L189">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="M189">
+        <v>3</v>
+      </c>
+      <c r="N189">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K190">
+        <v>589</v>
+      </c>
+      <c r="L190">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="M190">
+        <v>22</v>
+      </c>
+      <c r="N190">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="191" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K191">
+        <v>592</v>
+      </c>
+      <c r="L191">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="M191">
+        <v>11</v>
+      </c>
+      <c r="N191">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K192">
+        <v>594</v>
+      </c>
+      <c r="L192">
+        <f t="shared" si="12"/>
+        <v>23</v>
+      </c>
+      <c r="M192">
+        <v>12</v>
+      </c>
+      <c r="N192">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="193" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K193">
+        <v>596</v>
+      </c>
+      <c r="L193">
+        <f t="shared" si="12"/>
+        <v>17</v>
+      </c>
+      <c r="M193">
+        <v>17</v>
+      </c>
+      <c r="N193">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K194">
+        <v>598</v>
+      </c>
+      <c r="L194">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="M194">
+        <v>12</v>
+      </c>
+      <c r="N194">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="195" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K195">
+        <v>601</v>
+      </c>
+      <c r="L195">
+        <f t="shared" si="12"/>
+        <v>30</v>
+      </c>
+      <c r="M195">
+        <v>31</v>
+      </c>
+      <c r="N195">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="196" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K196">
+        <v>603</v>
+      </c>
+      <c r="L196">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="M196">
+        <v>19</v>
+      </c>
+      <c r="N196">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="197" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K197">
+        <v>606</v>
+      </c>
+      <c r="L197">
+        <f t="shared" si="12"/>
+        <v>49</v>
+      </c>
+      <c r="M197">
+        <v>49</v>
+      </c>
+      <c r="N197">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="198" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K198">
+        <v>609</v>
+      </c>
+      <c r="L198">
+        <f t="shared" si="12"/>
+        <v>44</v>
+      </c>
+      <c r="M198">
+        <v>40</v>
+      </c>
+      <c r="N198">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="199" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K199">
+        <v>612</v>
+      </c>
+      <c r="L199">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="M199">
+        <v>28</v>
+      </c>
+      <c r="N199">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K200">
+        <v>615</v>
+      </c>
+      <c r="L200">
+        <f t="shared" si="12"/>
+        <v>42</v>
+      </c>
+      <c r="M200">
+        <v>37</v>
+      </c>
+      <c r="N200">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="201" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K201">
+        <v>618</v>
+      </c>
+      <c r="L201">
+        <f t="shared" si="12"/>
+        <v>24</v>
+      </c>
+      <c r="M201">
+        <v>21</v>
+      </c>
+      <c r="N201">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="202" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K202">
+        <v>621</v>
+      </c>
+      <c r="L202">
+        <f t="shared" si="12"/>
+        <v>25</v>
+      </c>
+      <c r="M202">
+        <v>25</v>
+      </c>
+      <c r="N202">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="203" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K203">
+        <v>624</v>
+      </c>
+      <c r="L203">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="M203">
+        <v>23</v>
+      </c>
+      <c r="N203">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="204" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K204">
+        <v>627</v>
+      </c>
+      <c r="L204">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="M204">
+        <v>17</v>
+      </c>
+      <c r="N204">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="205" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K205">
+        <v>628</v>
+      </c>
+      <c r="L205">
+        <f t="shared" si="12"/>
+        <v>2</v>
+      </c>
+      <c r="M205">
+        <v>4</v>
+      </c>
+      <c r="N205">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K206">
+        <v>633</v>
+      </c>
+      <c r="L206">
+        <f t="shared" si="12"/>
+        <v>16</v>
+      </c>
+      <c r="M206">
+        <v>10</v>
+      </c>
+      <c r="N206">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="207" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K207">
+        <v>637</v>
+      </c>
+      <c r="L207">
+        <f t="shared" si="12"/>
+        <v>8</v>
+      </c>
+      <c r="M207">
+        <v>4</v>
+      </c>
+      <c r="N207">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K208">
+        <v>640</v>
+      </c>
+      <c r="L208">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="M208">
+        <v>6</v>
+      </c>
+      <c r="N208">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="209" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K209">
+        <v>645</v>
+      </c>
+      <c r="L209">
+        <f t="shared" si="12"/>
+        <v>20</v>
+      </c>
+      <c r="M209">
+        <v>20</v>
+      </c>
+      <c r="N209">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="210" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K210">
+        <v>648</v>
+      </c>
+      <c r="L210">
+        <f t="shared" si="12"/>
+        <v>22</v>
+      </c>
+      <c r="M210">
+        <v>20</v>
+      </c>
+      <c r="N210">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="211" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K211">
+        <v>651</v>
+      </c>
+      <c r="L211">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="M211">
+        <v>6</v>
+      </c>
+      <c r="N211">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K212">
+        <v>655</v>
+      </c>
+      <c r="L212">
+        <f t="shared" si="12"/>
+        <v>12</v>
+      </c>
+      <c r="M212">
+        <v>9</v>
+      </c>
+      <c r="N212">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K213">
+        <v>661</v>
+      </c>
+      <c r="L213">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="M213">
+        <v>13</v>
+      </c>
+      <c r="N213">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K214">
+        <v>664</v>
+      </c>
+      <c r="L214">
+        <f t="shared" si="12"/>
+        <v>13</v>
+      </c>
+      <c r="M214">
+        <v>12</v>
+      </c>
+      <c r="N214">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K215">
+        <v>669</v>
+      </c>
+      <c r="L215">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="M215">
+        <v>15</v>
+      </c>
+      <c r="N215">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="216" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K216">
+        <v>672</v>
+      </c>
+      <c r="L216">
+        <f t="shared" si="12"/>
+        <v>5</v>
+      </c>
+      <c r="M216">
+        <v>8</v>
+      </c>
+      <c r="N216">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="217" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K217">
+        <v>676</v>
+      </c>
+      <c r="L217">
+        <f t="shared" si="12"/>
+        <v>14</v>
+      </c>
+      <c r="M217">
+        <v>14</v>
+      </c>
+      <c r="N217">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="218" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K218">
+        <v>678</v>
+      </c>
+      <c r="L218">
+        <f t="shared" si="12"/>
+        <v>15</v>
+      </c>
+      <c r="M218">
+        <v>15</v>
+      </c>
+      <c r="N218">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="219" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K219">
+        <v>681</v>
+      </c>
+      <c r="L219">
+        <f t="shared" ref="L219:L250" si="13">VLOOKUP(K219,$D$2:$F$119,3,FALSE)</f>
+        <v>24</v>
+      </c>
+      <c r="M219">
+        <v>25</v>
+      </c>
+      <c r="N219">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K220">
+        <v>684</v>
+      </c>
+      <c r="L220">
+        <f t="shared" si="13"/>
+        <v>30</v>
+      </c>
+      <c r="M220">
+        <v>31</v>
+      </c>
+      <c r="N220">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="221" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K221">
+        <v>689</v>
+      </c>
+      <c r="L221">
+        <f t="shared" si="13"/>
+        <v>25</v>
+      </c>
+      <c r="M221">
+        <v>19</v>
+      </c>
+      <c r="N221">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="222" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K222">
+        <v>693</v>
+      </c>
+      <c r="L222">
+        <f t="shared" si="13"/>
+        <v>24</v>
+      </c>
+      <c r="M222">
+        <v>24</v>
+      </c>
+      <c r="N222">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="223" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K223">
+        <v>696</v>
+      </c>
+      <c r="L223">
+        <f t="shared" si="13"/>
+        <v>20</v>
+      </c>
+      <c r="M223">
+        <v>20</v>
+      </c>
+      <c r="N223">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="224" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K224">
+        <v>699</v>
+      </c>
+      <c r="L224">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="M224">
+        <v>12</v>
+      </c>
+      <c r="N224">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="225" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K225">
+        <v>702</v>
+      </c>
+      <c r="L225">
+        <f t="shared" si="13"/>
+        <v>8</v>
+      </c>
+      <c r="M225">
+        <v>4</v>
+      </c>
+      <c r="N225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K226">
+        <v>705</v>
+      </c>
+      <c r="L226">
+        <f t="shared" si="13"/>
+        <v>15</v>
+      </c>
+      <c r="M226">
+        <v>16</v>
+      </c>
+      <c r="N226">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="227" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K227">
+        <v>709</v>
+      </c>
+      <c r="L227">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="M227">
+        <v>18</v>
+      </c>
+      <c r="N227">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="228" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K228">
+        <v>712</v>
+      </c>
+      <c r="L228">
+        <f t="shared" si="13"/>
+        <v>4</v>
+      </c>
+      <c r="M228">
+        <v>2</v>
+      </c>
+      <c r="N228">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="229" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K229">
+        <v>716</v>
+      </c>
+      <c r="L229">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="M229">
+        <v>15</v>
+      </c>
+      <c r="N229">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="230" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K230">
+        <v>718</v>
+      </c>
+      <c r="L230">
+        <f t="shared" si="13"/>
+        <v>21</v>
+      </c>
+      <c r="M230">
+        <v>23</v>
+      </c>
+      <c r="N230">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="231" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K231">
+        <v>721</v>
+      </c>
+      <c r="L231">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="M231">
+        <v>16</v>
+      </c>
+      <c r="N231">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="232" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K232">
+        <v>723</v>
+      </c>
+      <c r="L232">
+        <f t="shared" si="13"/>
+        <v>19</v>
+      </c>
+      <c r="M232">
+        <v>26</v>
+      </c>
+      <c r="N232">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="233" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K233">
+        <v>725</v>
+      </c>
+      <c r="L233">
+        <f t="shared" si="13"/>
+        <v>13</v>
+      </c>
+      <c r="M233">
+        <v>18</v>
+      </c>
+      <c r="N233">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="234" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K234">
+        <v>728</v>
+      </c>
+      <c r="L234">
+        <f t="shared" si="13"/>
+        <v>23</v>
+      </c>
+      <c r="M234">
+        <v>18</v>
+      </c>
+      <c r="N234">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="235" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K235">
+        <v>731</v>
+      </c>
+      <c r="L235">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="M235">
+        <v>6</v>
+      </c>
+      <c r="N235">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="236" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K236">
+        <v>734</v>
+      </c>
+      <c r="L236">
+        <f t="shared" si="13"/>
+        <v>7</v>
+      </c>
+      <c r="M236">
+        <v>7</v>
+      </c>
+      <c r="N236">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="237" spans="11:14" x14ac:dyDescent="0.3">
+      <c r="K237">
+        <v>738</v>
+      </c>
+      <c r="L237">
+        <f t="shared" si="13"/>
+        <v>12</v>
+      </c>
+      <c r="M237">
+        <v>11</v>
+      </c>
+      <c r="N237">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="M3:Q118" xr:uid="{FBA55525-5725-432D-8CC7-0A0B7E5373EF}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="0.724637681"/>
-        <filter val="0.727272727"/>
-        <filter val="0.742857143"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="L3:S118" xr:uid="{FBA55525-5725-432D-8CC7-0A0B7E5373EF}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>